--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -16025,7 +16025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="39" min="1" max="2"/>
@@ -18626,416 +18626,733 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="66" t="inlineStr">
+      <c r="A112" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Samsung Batteries CP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Picked and dispatched by truck same-day tomorrow (22 Sep 2026); counted as met, not a genuine cutoff miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Made Group NZ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picked and dispatched by truck same-day tomorrow (22 Sep 2026); counted as met, not a genuine cutoff miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="75" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="66" t="inlineStr">
         <is>
           <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
         </is>
       </c>
     </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="64" t="inlineStr">
+    <row r="121"/>
+    <row r="122">
+      <c r="A122" s="64" t="inlineStr">
         <is>
           <t>Order Content-Based Overrides</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="65" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="65" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="39" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="39" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="B116" s="39" t="inlineStr">
+      <c r="B124" s="39" t="inlineStr">
         <is>
           <t>Delivery Company Name</t>
         </is>
       </c>
-      <c r="C116" s="39" t="inlineStr">
+      <c r="C124" s="39" t="inlineStr">
         <is>
           <t>farmers</t>
         </is>
       </c>
-      <c r="D116" s="39" t="inlineStr">
+      <c r="D124" s="39" t="inlineStr">
         <is>
           <t>Next Tuesday (17:00)</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="39" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="39" t="inlineStr">
         <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="B117" s="39" t="inlineStr">
+      <c r="B125" s="39" t="inlineStr">
         <is>
           <t>Delivery Company Name</t>
         </is>
       </c>
-      <c r="C117" s="39" t="inlineStr">
+      <c r="C125" s="39" t="inlineStr">
         <is>
           <t>briscoes</t>
         </is>
       </c>
-      <c r="D117" s="39" t="inlineStr">
+      <c r="D125" s="39" t="inlineStr">
         <is>
           <t>Next Tuesday (17:00)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="39" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="39" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="B118" s="39" t="inlineStr">
+      <c r="B126" s="39" t="inlineStr">
         <is>
           <t>Delivery Company Name</t>
         </is>
       </c>
-      <c r="C118" s="39" t="inlineStr">
+      <c r="C126" s="39" t="inlineStr">
         <is>
           <t>farmers</t>
         </is>
       </c>
-      <c r="D118" s="39" t="inlineStr">
+      <c r="D126" s="39" t="inlineStr">
         <is>
           <t>Next Monday (20:00)</t>
         </is>
       </c>
-      <c r="E118" s="75" t="n">
+      <c r="E126" s="75" t="n">
         <v>46251</v>
       </c>
-      <c r="F118" s="75" t="n">
+      <c r="F126" s="75" t="n">
         <v>46254</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="39" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="39" t="inlineStr">
         <is>
           <t>Gym Equip</t>
         </is>
       </c>
-      <c r="B119" s="39" t="inlineStr">
+      <c r="B127" s="39" t="inlineStr">
         <is>
           <t>All Orders</t>
         </is>
       </c>
-      <c r="C119" s="39" t="inlineStr">
+      <c r="C127" s="39" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="D119" s="39" t="inlineStr">
+      <c r="D127" s="39" t="inlineStr">
         <is>
           <t>Fixed (2026-09-02 20:00)</t>
         </is>
       </c>
-      <c r="E119" s="75" t="n"/>
-      <c r="F119" s="75" t="n">
+      <c r="E127" s="75" t="n"/>
+      <c r="F127" s="75" t="n">
         <v>46266</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="39" t="inlineStr">
         <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B128" s="39" t="inlineStr">
         <is>
           <t>Delivery Company Name</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C128" s="39" t="inlineStr">
         <is>
           <t>briscoes group</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D128" s="39" t="inlineStr">
         <is>
           <t>Fixed (2026-09-18 20:00)</t>
         </is>
       </c>
-      <c r="E120" s="75" t="n">
+      <c r="E128" s="75" t="n">
         <v>46280</v>
       </c>
-      <c r="F120" s="75" t="n">
+      <c r="F128" s="75" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="66" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>rebel sport</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="66" t="inlineStr">
         <is>
           <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="68" t="inlineStr">
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="69" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="69" t="inlineStr">
         <is>
           <t>Match Field</t>
         </is>
       </c>
-      <c r="F130" s="69" t="inlineStr">
+      <c r="F138" s="69" t="inlineStr">
         <is>
           <t>Attribute To</t>
         </is>
       </c>
-      <c r="G130" s="69" t="inlineStr">
+      <c r="G138" s="69" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="39" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="39" t="inlineStr">
         <is>
           <t>ShipTo</t>
         </is>
       </c>
-      <c r="B131" s="39" t="inlineStr">
+      <c r="B139" s="39" t="inlineStr">
         <is>
           <t>supercheap</t>
         </is>
       </c>
-      <c r="C131" s="39" t="inlineStr">
+      <c r="C139" s="39" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="F131" s="39" t="inlineStr">
+      <c r="F139" s="39" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="G131" s="70" t="inlineStr">
+      <c r="G139" s="70" t="inlineStr">
         <is>
           <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="39" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="39" t="inlineStr">
         <is>
           <t>ShipTo</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="39" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B133" s="39" t="inlineStr">
-        <is>
-          <t>srg</t>
-        </is>
-      </c>
-      <c r="C133" s="39" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F133" s="39" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G133" s="70" t="inlineStr">
-        <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="39" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B134" s="39" t="inlineStr">
-        <is>
-          <t>repco</t>
-        </is>
-      </c>
-      <c r="C134" s="39" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F134" s="39" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G134" s="70" t="inlineStr">
-        <is>
-          <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="71" t="inlineStr">
-        <is>
-          <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="68" t="inlineStr">
-        <is>
-          <t>Table 5: International Carrier SLAs</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="69" t="inlineStr">
-        <is>
-          <t>Service Code</t>
-        </is>
-      </c>
-      <c r="B140" s="69" t="inlineStr">
-        <is>
-          <t>Destination</t>
-        </is>
-      </c>
-      <c r="C140" s="69" t="inlineStr">
-        <is>
-          <t>Business Days</t>
-        </is>
-      </c>
-      <c r="D140" s="69" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E140" s="69" t="inlineStr">
-        <is>
-          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="39" t="inlineStr">
         <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B141" s="39" t="inlineStr">
+        <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C141" s="39" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F141" s="39" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G141" s="70" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="39" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B142" s="39" t="inlineStr">
+        <is>
+          <t>repco</t>
+        </is>
+      </c>
+      <c r="C142" s="39" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F142" s="39" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G142" s="70" t="inlineStr">
+        <is>
+          <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" s="71" t="inlineStr">
+        <is>
+          <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147">
+      <c r="A147" s="68" t="inlineStr">
+        <is>
+          <t>Table 5: International Carrier SLAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="69" t="inlineStr">
+        <is>
+          <t>Service Code</t>
+        </is>
+      </c>
+      <c r="B148" s="69" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="C148" s="69" t="inlineStr">
+        <is>
+          <t>Business Days</t>
+        </is>
+      </c>
+      <c r="D148" s="69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E148" s="69" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="39" t="inlineStr">
+        <is>
           <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
         </is>
       </c>
-      <c r="B141" s="39" t="inlineStr">
+      <c r="B149" s="39" t="inlineStr">
         <is>
           <t>All international</t>
         </is>
       </c>
-      <c r="C141" s="39" t="n">
+      <c r="C149" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="D141" s="39" t="inlineStr">
+      <c r="D149" s="39" t="inlineStr">
         <is>
           <t>fedex.com/en-nz</t>
         </is>
       </c>
-      <c r="E141" s="70" t="inlineStr">
+      <c r="E149" s="70" t="inlineStr">
         <is>
           <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="71" t="inlineStr">
+    <row r="150"/>
+    <row r="151">
+      <c r="A151" s="71" t="inlineStr">
         <is>
           <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="39" t="inlineStr">
-        <is>
-          <t>Table 6: Public Holidays</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B147" s="39" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="72" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B148" s="39" t="inlineStr">
-        <is>
-          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="75" t="n"/>
-      <c r="B149" s="39" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="39" t="inlineStr">
-        <is>
-          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="39" t="inlineStr">
-        <is>
-          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
-        </is>
-      </c>
-    </row>
+    <row r="152"/>
+    <row r="153"/>
     <row r="154">
       <c r="A154" s="39" t="inlineStr">
         <is>
+          <t>Table 6: Public Holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="39" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B154" s="39" t="inlineStr">
+      <c r="B155" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="72" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B156" s="39" t="inlineStr">
+        <is>
+          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="75" t="n"/>
+      <c r="B157" s="39" t="n"/>
+    </row>
+    <row r="158"/>
+    <row r="159">
+      <c r="A159" s="39" t="inlineStr">
+        <is>
+          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160"/>
+    <row r="161">
+      <c r="A161" s="39" t="inlineStr">
+        <is>
+          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B162" s="39" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="75" t="n">
+    <row r="163">
+      <c r="A163" s="75" t="n">
         <v>46244</v>
       </c>
-      <c r="B155" s="39" t="inlineStr">
+      <c r="B163" s="39" t="inlineStr">
         <is>
           <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="39" t="inlineStr">
+    <row r="164"/>
+    <row r="165">
+      <c r="A165" s="39" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>
@@ -19234,255 +19551,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CB702797C59B384BA5825BD7F91C8FA6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed5aae9864b7dcbba9993313f29ed662">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e670929-1bdc-480c-8510-e43a2a862a6e" xmlns:ns3="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a292da2c54c23b9d44e0544df2ef32" ns2:_="" ns3:_="">
-    <xsd:import namespace="7e670929-1bdc-480c-8510-e43a2a862a6e"/>
-    <xsd:import namespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:Access" minOccurs="0"/>
-                <xsd:element ref="ns2:Access_x002f_Info" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e670929-1bdc-480c-8510-e43a2a862a6e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b25c28e6-01a0-48d2-b828-62504f505dd7" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Access" ma:index="18" nillable="true" ma:displayName="Access" ma:description="Who gets access&#10;" ma:format="Dropdown" ma:internalName="Access">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Access_x002f_Info" ma:index="19" nillable="true" ma:displayName="Access/ Info " ma:format="Dropdown" ma:internalName="Access_x002f_Info">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{156fa16d-c7d6-4694-aac4-2bac9e86d8b0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Access xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" xsi:nil="true"/>
-    <Access_x002f_Info xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D47624E-4852-412B-BB30-A015991298E1}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0D34DCA-42E2-4205-B659-6549C51CEC19}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FF7BC3D-B7B7-4F41-B9CF-0B8B22B60CB0}"/>
 </file>
--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -16025,7 +16025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="39" min="1" max="2"/>
@@ -16042,7 +16042,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="34">
       <c r="A3" s="64" t="inlineStr">
         <is>
@@ -16253,11 +16252,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="34">
       <c r="A15" s="66" t="inlineStr">
         <is>
@@ -16265,7 +16259,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="34">
       <c r="A17" s="64" t="inlineStr">
         <is>
@@ -16915,10 +16908,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="72" t="n">
         <v>46196</v>
@@ -18626,733 +18615,415 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Samsung Batteries CP</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
+      <c r="A112" s="66" t="inlineStr">
+        <is>
+          <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="64" t="inlineStr">
+        <is>
+          <t>Order Content-Based Overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="65" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="39" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B116" s="39" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D116" s="39" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="39" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="B117" s="39" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>briscoes</t>
+        </is>
+      </c>
+      <c r="D117" s="39" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="39" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B118" s="39" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D118" s="39" t="inlineStr">
+        <is>
+          <t>Next Monday (20:00)</t>
+        </is>
+      </c>
+      <c r="E118" s="75" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F118" s="75" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="39" t="inlineStr">
+        <is>
+          <t>Gym Equip</t>
+        </is>
+      </c>
+      <c r="B119" s="39" t="inlineStr">
+        <is>
+          <t>All Orders</t>
+        </is>
+      </c>
+      <c r="C119" s="39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D119" s="39" t="inlineStr">
+        <is>
+          <t>Fixed (2026-09-02 20:00)</t>
+        </is>
+      </c>
+      <c r="E119" s="75" t="n"/>
+      <c r="F119" s="75" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="39" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="B120" s="39" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>briscoes group</t>
+        </is>
+      </c>
+      <c r="D120" s="39" t="inlineStr">
+        <is>
+          <t>Fixed (2026-09-18 20:00)</t>
+        </is>
+      </c>
+      <c r="E120" s="75" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F120" s="75" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="66" t="inlineStr">
+        <is>
+          <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="68" t="inlineStr">
+        <is>
+          <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="69" t="inlineStr">
+        <is>
+          <t>Match Field</t>
+        </is>
+      </c>
+      <c r="F130" s="69" t="inlineStr">
+        <is>
+          <t>Attribute To</t>
+        </is>
+      </c>
+      <c r="G130" s="69" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="39" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B131" s="39" t="inlineStr">
+        <is>
+          <t>supercheap</t>
+        </is>
+      </c>
+      <c r="C131" s="39" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Picked and dispatched by truck same-day tomorrow (22 Sep 2026); counted as met, not a genuine cutoff miss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Made Group NZ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>4588</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="F131" s="39" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G131" s="70" t="inlineStr">
+        <is>
+          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="39" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="39" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B133" s="39" t="inlineStr">
+        <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C133" s="39" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Picked and dispatched by truck same-day tomorrow (22 Sep 2026); counted as met, not a genuine cutoff miss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
+      <c r="F133" s="39" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G133" s="70" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="39" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B134" s="39" t="inlineStr">
+        <is>
+          <t>repco</t>
+        </is>
+      </c>
+      <c r="C134" s="39" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>4593</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="75" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Ships via Briscoes/Rebel Sport Delivery Company Name override (Next Tuesday 17:00 deadline) which was not applied in the calculation - counted as met per operations review; underlying calc issue being investigated separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="66" t="inlineStr">
-        <is>
-          <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121"/>
-    <row r="122">
-      <c r="A122" s="64" t="inlineStr">
-        <is>
-          <t>Order Content-Based Overrides</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="65" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="39" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B124" s="39" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C124" s="39" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D124" s="39" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="39" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="B125" s="39" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C125" s="39" t="inlineStr">
-        <is>
-          <t>briscoes</t>
-        </is>
-      </c>
-      <c r="D125" s="39" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="39" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B126" s="39" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C126" s="39" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D126" s="39" t="inlineStr">
-        <is>
-          <t>Next Monday (20:00)</t>
-        </is>
-      </c>
-      <c r="E126" s="75" t="n">
-        <v>46251</v>
-      </c>
-      <c r="F126" s="75" t="n">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="39" t="inlineStr">
-        <is>
-          <t>Gym Equip</t>
-        </is>
-      </c>
-      <c r="B127" s="39" t="inlineStr">
-        <is>
-          <t>All Orders</t>
-        </is>
-      </c>
-      <c r="C127" s="39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D127" s="39" t="inlineStr">
-        <is>
-          <t>Fixed (2026-09-02 20:00)</t>
-        </is>
-      </c>
-      <c r="E127" s="75" t="n"/>
-      <c r="F127" s="75" t="n">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="39" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="B128" s="39" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C128" s="39" t="inlineStr">
-        <is>
-          <t>briscoes group</t>
-        </is>
-      </c>
-      <c r="D128" s="39" t="inlineStr">
-        <is>
-          <t>Fixed (2026-09-18 20:00)</t>
-        </is>
-      </c>
-      <c r="E128" s="75" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F128" s="75" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>rebel sport</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134">
-      <c r="A134" s="66" t="inlineStr">
-        <is>
-          <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137">
-      <c r="A137" s="68" t="inlineStr">
-        <is>
-          <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="69" t="inlineStr">
-        <is>
-          <t>Match Field</t>
-        </is>
-      </c>
-      <c r="F138" s="69" t="inlineStr">
-        <is>
-          <t>Attribute To</t>
-        </is>
-      </c>
-      <c r="G138" s="69" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="F134" s="39" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G134" s="70" t="inlineStr">
+        <is>
+          <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="71" t="inlineStr">
+        <is>
+          <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="39" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B139" s="39" t="inlineStr">
-        <is>
-          <t>supercheap</t>
-        </is>
-      </c>
-      <c r="C139" s="39" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F139" s="39" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G139" s="70" t="inlineStr">
-        <is>
-          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
+      <c r="A139" s="68" t="inlineStr">
+        <is>
+          <t>Table 5: International Carrier SLAs</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="39" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
+      <c r="A140" s="69" t="inlineStr">
+        <is>
+          <t>Service Code</t>
+        </is>
+      </c>
+      <c r="B140" s="69" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="C140" s="69" t="inlineStr">
+        <is>
+          <t>Business Days</t>
+        </is>
+      </c>
+      <c r="D140" s="69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E140" s="69" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="39" t="inlineStr">
         <is>
-          <t>ShipTo</t>
+          <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
         </is>
       </c>
       <c r="B141" s="39" t="inlineStr">
         <is>
-          <t>srg</t>
-        </is>
-      </c>
-      <c r="C141" s="39" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F141" s="39" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G141" s="70" t="inlineStr">
-        <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="39" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B142" s="39" t="inlineStr">
-        <is>
-          <t>repco</t>
-        </is>
-      </c>
-      <c r="C142" s="39" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F142" s="39" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G142" s="70" t="inlineStr">
-        <is>
-          <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" s="71" t="inlineStr">
-        <is>
-          <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145"/>
-    <row r="146"/>
+          <t>All international</t>
+        </is>
+      </c>
+      <c r="C141" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D141" s="39" t="inlineStr">
+        <is>
+          <t>fedex.com/en-nz</t>
+        </is>
+      </c>
+      <c r="E141" s="70" t="inlineStr">
+        <is>
+          <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="71" t="inlineStr">
+        <is>
+          <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="39" t="inlineStr">
+        <is>
+          <t>Table 6: Public Holidays</t>
+        </is>
+      </c>
+    </row>
     <row r="147">
-      <c r="A147" s="68" t="inlineStr">
-        <is>
-          <t>Table 5: International Carrier SLAs</t>
+      <c r="A147" s="39" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B147" s="39" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="69" t="inlineStr">
-        <is>
-          <t>Service Code</t>
-        </is>
-      </c>
-      <c r="B148" s="69" t="inlineStr">
-        <is>
-          <t>Destination</t>
-        </is>
-      </c>
-      <c r="C148" s="69" t="inlineStr">
-        <is>
-          <t>Business Days</t>
-        </is>
-      </c>
-      <c r="D148" s="69" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E148" s="69" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A148" s="72" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B148" s="39" t="inlineStr">
+        <is>
+          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="39" t="inlineStr">
-        <is>
-          <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
-        </is>
-      </c>
-      <c r="B149" s="39" t="inlineStr">
-        <is>
-          <t>All international</t>
-        </is>
-      </c>
-      <c r="C149" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D149" s="39" t="inlineStr">
-        <is>
-          <t>fedex.com/en-nz</t>
-        </is>
-      </c>
-      <c r="E149" s="70" t="inlineStr">
-        <is>
-          <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="150"/>
+      <c r="A149" s="75" t="n"/>
+      <c r="B149" s="39" t="n"/>
+    </row>
     <row r="151">
-      <c r="A151" s="71" t="inlineStr">
-        <is>
-          <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152"/>
-    <row r="153"/>
+      <c r="A151" s="39" t="inlineStr">
+        <is>
+          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="39" t="inlineStr">
+        <is>
+          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+        </is>
+      </c>
+    </row>
     <row r="154">
       <c r="A154" s="39" t="inlineStr">
         <is>
-          <t>Table 6: Public Holidays</t>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B154" s="39" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
+      <c r="A155" s="75" t="n">
+        <v>46244</v>
       </c>
       <c r="B155" s="39" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="72" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B156" s="39" t="inlineStr">
-        <is>
-          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
+          <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="75" t="n"/>
-      <c r="B157" s="39" t="n"/>
-    </row>
-    <row r="158"/>
-    <row r="159">
-      <c r="A159" s="39" t="inlineStr">
-        <is>
-          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160"/>
-    <row r="161">
-      <c r="A161" s="39" t="inlineStr">
-        <is>
-          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="39" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B162" s="39" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="75" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B163" s="39" t="inlineStr">
-        <is>
-          <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
-        </is>
-      </c>
-    </row>
-    <row r="164"/>
-    <row r="165">
-      <c r="A165" s="39" t="inlineStr">
+      <c r="A157" s="39" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>
@@ -19379,7 +19050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="34" min="1" max="1"/>
@@ -19545,10 +19216,284 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="75" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Missing item - 1x unit of V1561BL2 not sent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CB702797C59B384BA5825BD7F91C8FA6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed5aae9864b7dcbba9993313f29ed662">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e670929-1bdc-480c-8510-e43a2a862a6e" xmlns:ns3="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a292da2c54c23b9d44e0544df2ef32" ns2:_="" ns3:_="">
+    <xsd:import namespace="7e670929-1bdc-480c-8510-e43a2a862a6e"/>
+    <xsd:import namespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:Access" minOccurs="0"/>
+                <xsd:element ref="ns2:Access_x002f_Info" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e670929-1bdc-480c-8510-e43a2a862a6e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b25c28e6-01a0-48d2-b828-62504f505dd7" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Access" ma:index="18" nillable="true" ma:displayName="Access" ma:description="Who gets access&#10;" ma:format="Dropdown" ma:internalName="Access">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Access_x002f_Info" ma:index="19" nillable="true" ma:displayName="Access/ Info " ma:format="Dropdown" ma:internalName="Access_x002f_Info">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{156fa16d-c7d6-4694-aac4-2bac9e86d8b0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Access xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" xsi:nil="true"/>
+    <Access_x002f_Info xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{738DE68F-1409-4F45-BEEC-8D454DF8C62B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9885CC80-D5B3-4EE8-BC70-F4AAED59DFC4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78136DF6-6868-4D47-AEB4-2272E116F3EC}"/>
 </file>
--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -19050,7 +19050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="34" min="1" max="1"/>
@@ -19220,22 +19220,45 @@
       <c r="A10" s="75" t="n">
         <v>46287</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>3331</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Missing item - 1x unit of V1561BL2 not sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="75" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Wrong product picked - 4x Bamboo Laced sent instead of Scalloped</t>
         </is>
       </c>
     </row>
@@ -19487,13 +19510,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{738DE68F-1409-4F45-BEEC-8D454DF8C62B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CDB5739-B8FA-4BE3-9BC6-36C2BE51D9A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9885CC80-D5B3-4EE8-BC70-F4AAED59DFC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C18CBA2-404E-4165-B1C5-406B08DD27D4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78136DF6-6868-4D47-AEB4-2272E116F3EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA5A7C5E-357D-4004-948F-A20A57EC9772}"/>
 </file>
--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -27,13 +27,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;General;General"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -17234,30 +17235,30 @@
       <c r="A352" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="49" t="inlineStr">
         <is>
           <t>Aleger Studio</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C352" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E352" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F352" t="n">
+      <c r="E352" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F352" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G352" t="n">
+      <c r="G352" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H352">
+      <c r="H352" s="49">
         <f>F352/G352</f>
         <v/>
       </c>
-      <c r="I352">
+      <c r="I352" s="49">
         <f>IF(H352&gt;=E352,"Yes","No")</f>
         <v/>
       </c>
@@ -17266,34 +17267,34 @@
       <c r="A353" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="49" t="inlineStr">
         <is>
           <t>Coromandel Mountains Company Limited</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E353" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F353" t="n">
+      <c r="E353" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F353" s="49" t="n">
         <v>32</v>
       </c>
-      <c r="G353" t="n">
+      <c r="G353" s="49" t="n">
         <v>34</v>
       </c>
-      <c r="H353">
+      <c r="H353" s="49">
         <f>F353/G353</f>
         <v/>
       </c>
-      <c r="I353">
+      <c r="I353" s="49">
         <f>IF(H353&gt;=E353,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J353" t="inlineStr">
+      <c r="J353" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17303,34 +17304,34 @@
       <c r="A354" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="49" t="inlineStr">
         <is>
           <t>EcoPallets</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E354" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F354" t="n">
+      <c r="E354" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F354" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="G354" t="n">
+      <c r="G354" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="H354">
+      <c r="H354" s="49">
         <f>F354/G354</f>
         <v/>
       </c>
-      <c r="I354">
+      <c r="I354" s="49">
         <f>IF(H354&gt;=E354,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J354" t="inlineStr">
+      <c r="J354" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17340,34 +17341,34 @@
       <c r="A355" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="49" t="inlineStr">
         <is>
           <t>Flo &amp; Frankie</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E355" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F355" t="n">
+      <c r="E355" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F355" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="G355" t="n">
+      <c r="G355" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="H355">
+      <c r="H355" s="49">
         <f>F355/G355</f>
         <v/>
       </c>
-      <c r="I355">
+      <c r="I355" s="49">
         <f>IF(H355&gt;=E355,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J355" t="inlineStr">
+      <c r="J355" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17377,34 +17378,34 @@
       <c r="A356" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="49" t="inlineStr">
         <is>
           <t>Gym Equip</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E356" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F356" t="n">
+      <c r="E356" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F356" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="G356" t="n">
+      <c r="G356" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="H356">
+      <c r="H356" s="49">
         <f>F356/G356</f>
         <v/>
       </c>
-      <c r="I356">
+      <c r="I356" s="49">
         <f>IF(H356&gt;=E356,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J356" t="inlineStr">
+      <c r="J356" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17414,30 +17415,30 @@
       <c r="A357" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B357" s="49" t="inlineStr">
         <is>
           <t>Interior Images</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E357" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F357" t="n">
+      <c r="E357" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F357" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G357" t="n">
+      <c r="G357" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H357">
+      <c r="H357" s="49">
         <f>F357/G357</f>
         <v/>
       </c>
-      <c r="I357">
+      <c r="I357" s="49">
         <f>IF(H357&gt;=E357,"Yes","No")</f>
         <v/>
       </c>
@@ -17446,34 +17447,34 @@
       <c r="A358" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="49" t="inlineStr">
         <is>
           <t>Jock Freight - SECA</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E358" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F358" t="n">
+      <c r="E358" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F358" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="G358" t="n">
+      <c r="G358" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="H358">
+      <c r="H358" s="49">
         <f>F358/G358</f>
         <v/>
       </c>
-      <c r="I358">
+      <c r="I358" s="49">
         <f>IF(H358&gt;=E358,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J358" t="inlineStr">
+      <c r="J358" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17483,30 +17484,30 @@
       <c r="A359" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="49" t="inlineStr">
         <is>
           <t>Logwin - Sikla</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E359" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F359" t="n">
+      <c r="E359" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F359" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G359" t="n">
+      <c r="G359" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H359">
+      <c r="H359" s="49">
         <f>F359/G359</f>
         <v/>
       </c>
-      <c r="I359">
+      <c r="I359" s="49">
         <f>IF(H359&gt;=E359,"Yes","No")</f>
         <v/>
       </c>
@@ -17515,30 +17516,30 @@
       <c r="A360" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B360" s="49" t="inlineStr">
         <is>
           <t>Made Group NZ</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E360" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F360" t="n">
+      <c r="E360" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F360" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G360" t="n">
+      <c r="G360" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H360">
+      <c r="H360" s="49">
         <f>F360/G360</f>
         <v/>
       </c>
-      <c r="I360">
+      <c r="I360" s="49">
         <f>IF(H360&gt;=E360,"Yes","No")</f>
         <v/>
       </c>
@@ -17547,30 +17548,30 @@
       <c r="A361" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B361" s="49" t="inlineStr">
         <is>
           <t>May Eleven NZ</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E361" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F361" t="n">
+      <c r="E361" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F361" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G361" t="n">
+      <c r="G361" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="H361">
+      <c r="H361" s="49">
         <f>F361/G361</f>
         <v/>
       </c>
-      <c r="I361">
+      <c r="I361" s="49">
         <f>IF(H361&gt;=E361,"Yes","No")</f>
         <v/>
       </c>
@@ -17579,34 +17580,34 @@
       <c r="A362" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B362" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E362" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F362" t="n">
+      <c r="E362" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F362" s="49" t="n">
         <v>75</v>
       </c>
-      <c r="G362" t="n">
+      <c r="G362" s="49" t="n">
         <v>79</v>
       </c>
-      <c r="H362">
+      <c r="H362" s="49">
         <f>F362/G362</f>
         <v/>
       </c>
-      <c r="I362">
+      <c r="I362" s="49">
         <f>IF(H362&gt;=E362,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J362" t="inlineStr">
+      <c r="J362" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17616,30 +17617,30 @@
       <c r="A363" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B363" s="49" t="inlineStr">
         <is>
           <t>Purify Me</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E363" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F363" t="n">
+      <c r="E363" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F363" s="49" t="n">
         <v>46</v>
       </c>
-      <c r="G363" t="n">
+      <c r="G363" s="49" t="n">
         <v>48</v>
       </c>
-      <c r="H363">
+      <c r="H363" s="49">
         <f>F363/G363</f>
         <v/>
       </c>
-      <c r="I363">
+      <c r="I363" s="49">
         <f>IF(H363&gt;=E363,"Yes","No")</f>
         <v/>
       </c>
@@ -17648,30 +17649,30 @@
       <c r="A364" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B364" s="49" t="inlineStr">
         <is>
           <t>Salt Shark</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E364" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F364" t="n">
+      <c r="E364" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F364" s="49" t="n">
         <v>38</v>
       </c>
-      <c r="G364" t="n">
+      <c r="G364" s="49" t="n">
         <v>39</v>
       </c>
-      <c r="H364">
+      <c r="H364" s="49">
         <f>F364/G364</f>
         <v/>
       </c>
-      <c r="I364">
+      <c r="I364" s="49">
         <f>IF(H364&gt;=E364,"Yes","No")</f>
         <v/>
       </c>
@@ -17680,34 +17681,34 @@
       <c r="A365" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="49" t="inlineStr">
         <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E365" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F365" t="n">
+      <c r="E365" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F365" s="49" t="n">
         <v>81</v>
       </c>
-      <c r="G365" t="n">
+      <c r="G365" s="49" t="n">
         <v>88</v>
       </c>
-      <c r="H365">
+      <c r="H365" s="49">
         <f>F365/G365</f>
         <v/>
       </c>
-      <c r="I365">
+      <c r="I365" s="49">
         <f>IF(H365&gt;=E365,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J365" t="inlineStr">
+      <c r="J365" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17717,30 +17718,30 @@
       <c r="A366" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="49" t="inlineStr">
         <is>
           <t>Stryx</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E366" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F366" t="n">
+      <c r="E366" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F366" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="G366" t="n">
+      <c r="G366" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="H366">
+      <c r="H366" s="49">
         <f>F366/G366</f>
         <v/>
       </c>
-      <c r="I366">
+      <c r="I366" s="49">
         <f>IF(H366&gt;=E366,"Yes","No")</f>
         <v/>
       </c>
@@ -17749,34 +17750,34 @@
       <c r="A367" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="49" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E367" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F367" t="n">
+      <c r="E367" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F367" s="49" t="n">
         <v>162</v>
       </c>
-      <c r="G367" t="n">
+      <c r="G367" s="49" t="n">
         <v>172</v>
       </c>
-      <c r="H367">
+      <c r="H367" s="49">
         <f>F367/G367</f>
         <v/>
       </c>
-      <c r="I367">
+      <c r="I367" s="49">
         <f>IF(H367&gt;=E367,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J367" t="inlineStr">
+      <c r="J367" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17807,7 +17808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="49" min="1" max="2"/>
@@ -18688,10 +18689,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="50">
       <c r="A40" s="77" t="n">
         <v>46196</v>
@@ -20402,32 +20399,32 @@
       <c r="A112" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="49" t="inlineStr">
         <is>
           <t>HL085007</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G112" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20437,32 +20434,32 @@
       <c r="A113" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="49" t="inlineStr">
         <is>
           <t>4522201808</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G113" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20472,32 +20469,32 @@
       <c r="A114" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="49" t="inlineStr">
         <is>
           <t>S 122 127866</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G114" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20507,32 +20504,32 @@
       <c r="A115" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="49" t="inlineStr">
         <is>
           <t>4522172931</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20542,32 +20539,32 @@
       <c r="A116" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="49" t="inlineStr">
         <is>
           <t>4522133734</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G116" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20577,32 +20574,32 @@
       <c r="A117" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="49" t="inlineStr">
         <is>
           <t>4522087338</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20612,100 +20609,126 @@
       <c r="A118" s="90" t="n">
         <v>46295</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="49" t="inlineStr">
         <is>
           <t>4707052687</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="50">
-      <c r="A119" s="84" t="inlineStr">
+      <c r="A119" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B119" s="49" t="inlineStr">
+        <is>
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C119" s="49" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="D119" s="49" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E119" s="49" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F119" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G119" s="49" t="inlineStr">
+        <is>
+          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) — extension approved, not a genuine cutoff miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="50">
+      <c r="A120" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B120" s="49" t="inlineStr">
+        <is>
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C120" s="49" t="inlineStr">
+        <is>
+          <t>4953</t>
+        </is>
+      </c>
+      <c r="D120" s="49" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E120" s="49" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F120" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G120" s="49" t="inlineStr">
+        <is>
+          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) — extension approved, not a genuine cutoff miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="84" t="inlineStr">
         <is>
           <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="50"/>
-    <row r="121">
-      <c r="A121" s="81" t="inlineStr">
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" s="81" t="inlineStr">
         <is>
           <t>Order Content-Based Overrides</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="82" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="82" t="inlineStr">
         <is>
           <t>Customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="49" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B123" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C123" s="49" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D123" s="49" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="49" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="B124" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C124" s="49" t="inlineStr">
-        <is>
-          <t>briscoes</t>
-        </is>
-      </c>
-      <c r="D124" s="49" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
         </is>
       </c>
     </row>
@@ -20727,139 +20750,149 @@
       </c>
       <c r="D125" s="49" t="inlineStr">
         <is>
-          <t>Next Monday (20:00)</t>
-        </is>
-      </c>
-      <c r="E125" s="83" t="n">
-        <v>46251</v>
-      </c>
-      <c r="F125" s="83" t="n">
-        <v>46254</v>
+          <t>Next Tuesday (17:00)</t>
+        </is>
       </c>
     </row>
     <row r="126" ht="126.85" customHeight="1" s="50">
       <c r="A126" s="49" t="inlineStr">
         <is>
-          <t>Gym Equip</t>
+          <t>Simply Clean</t>
         </is>
       </c>
       <c r="B126" s="49" t="inlineStr">
         <is>
-          <t>All Orders</t>
+          <t>Delivery Company Name</t>
         </is>
       </c>
       <c r="C126" s="49" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>briscoes</t>
         </is>
       </c>
       <c r="D126" s="49" t="inlineStr">
         <is>
-          <t>Fixed (2026-09-02 20:00)</t>
-        </is>
-      </c>
-      <c r="E126" s="83" t="n"/>
-      <c r="F126" s="83" t="n">
-        <v>46266</v>
+          <t>Next Tuesday (17:00)</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="49" t="inlineStr">
         <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B127" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C127" s="49" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D127" s="49" t="inlineStr">
+        <is>
+          <t>Next Monday (20:00)</t>
+        </is>
+      </c>
+      <c r="E127" s="83" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F127" s="83" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="49" t="inlineStr">
+        <is>
+          <t>Gym Equip</t>
+        </is>
+      </c>
+      <c r="B128" s="49" t="inlineStr">
+        <is>
+          <t>All Orders</t>
+        </is>
+      </c>
+      <c r="C128" s="49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D128" s="49" t="inlineStr">
+        <is>
+          <t>Fixed (2026-09-02 20:00)</t>
+        </is>
+      </c>
+      <c r="E128" s="83" t="n"/>
+      <c r="F128" s="83" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="50">
+      <c r="A129" s="49" t="inlineStr">
+        <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="B127" s="49" t="inlineStr">
+      <c r="B129" s="49" t="inlineStr">
         <is>
           <t>Delivery Company Name</t>
         </is>
       </c>
-      <c r="C127" s="49" t="inlineStr">
+      <c r="C129" s="49" t="inlineStr">
         <is>
           <t>briscoes group</t>
         </is>
       </c>
-      <c r="D127" s="49" t="inlineStr">
+      <c r="D129" s="49" t="inlineStr">
         <is>
           <t>Fixed (2026-09-18 20:00)</t>
         </is>
       </c>
-      <c r="E127" s="83" t="n">
+      <c r="E129" s="83" t="n">
         <v>46280</v>
       </c>
-      <c r="F127" s="83" t="n">
+      <c r="F129" s="83" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="128"/>
-    <row r="129" ht="15" customHeight="1" s="50"/>
     <row r="130" ht="15" customHeight="1" s="50"/>
     <row r="131" ht="23.85" customHeight="1" s="50"/>
     <row r="132" ht="15" customHeight="1" s="50"/>
-    <row r="133" ht="23.85" customHeight="1" s="50">
-      <c r="A133" s="84" t="inlineStr">
+    <row r="133" ht="23.85" customHeight="1" s="50"/>
+    <row r="134" ht="23.85" customHeight="1" s="50"/>
+    <row r="135">
+      <c r="A135" s="84" t="inlineStr">
         <is>
           <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="23.85" customHeight="1" s="50"/>
-    <row r="135"/>
-    <row r="136" ht="99.95" customHeight="1" s="50">
-      <c r="A136" s="85" t="inlineStr">
+    <row r="136" ht="99.95" customHeight="1" s="50"/>
+    <row r="137"/>
+    <row r="138">
+      <c r="A138" s="85" t="inlineStr">
         <is>
           <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="86" t="inlineStr">
+    <row r="139" ht="15" customHeight="1" s="50">
+      <c r="A139" s="86" t="inlineStr">
         <is>
           <t>Match Field</t>
         </is>
       </c>
-      <c r="F137" s="86" t="inlineStr">
+      <c r="F139" s="86" t="inlineStr">
         <is>
           <t>Attribute To</t>
         </is>
       </c>
-      <c r="G137" s="86" t="inlineStr">
+      <c r="G139" s="86" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B138" s="49" t="inlineStr">
-        <is>
-          <t>supercheap</t>
-        </is>
-      </c>
-      <c r="C138" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F138" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G138" s="69" t="inlineStr">
-        <is>
-          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="50">
-      <c r="A139" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
         </is>
       </c>
     </row>
@@ -20871,7 +20904,7 @@
       </c>
       <c r="B140" s="49" t="inlineStr">
         <is>
-          <t>srg</t>
+          <t>supercheap</t>
         </is>
       </c>
       <c r="C140" s="49" t="inlineStr">
@@ -20886,7 +20919,7 @@
       </c>
       <c r="G140" s="69" t="inlineStr">
         <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
         </is>
       </c>
     </row>
@@ -20896,179 +20929,213 @@
           <t>ShipTo</t>
         </is>
       </c>
-      <c r="B141" s="49" t="inlineStr">
+    </row>
+    <row r="142">
+      <c r="A142" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B142" s="49" t="inlineStr">
+        <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C142" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F142" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G142" s="69" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="46.25" customHeight="1" s="50">
+      <c r="A143" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B143" s="49" t="inlineStr">
         <is>
           <t>repco</t>
         </is>
       </c>
-      <c r="C141" s="49" t="inlineStr">
+      <c r="C143" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="F141" s="49" t="inlineStr">
+      <c r="F143" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="G141" s="69" t="inlineStr">
+      <c r="G143" s="69" t="inlineStr">
         <is>
           <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
-    <row r="142"/>
-    <row r="143" ht="46.25" customHeight="1" s="50">
-      <c r="A143" s="87" t="inlineStr">
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="87" t="inlineStr">
         <is>
           <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
         </is>
       </c>
     </row>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146" ht="15" customHeight="1" s="50">
-      <c r="A146" s="85" t="inlineStr">
+    <row r="146" ht="15" customHeight="1" s="50"/>
+    <row r="147" ht="15" customHeight="1" s="50"/>
+    <row r="148" ht="15" customHeight="1" s="50">
+      <c r="A148" s="85" t="inlineStr">
         <is>
           <t>Table 5: International Carrier SLAs</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1" s="50">
-      <c r="A147" s="86" t="inlineStr">
+    <row r="149" ht="15" customHeight="1" s="50">
+      <c r="A149" s="86" t="inlineStr">
         <is>
           <t>Service Code</t>
         </is>
       </c>
-      <c r="B147" s="86" t="inlineStr">
+      <c r="B149" s="86" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="C147" s="86" t="inlineStr">
+      <c r="C149" s="86" t="inlineStr">
         <is>
           <t>Business Days</t>
         </is>
       </c>
-      <c r="D147" s="86" t="inlineStr">
+      <c r="D149" s="86" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E147" s="86" t="inlineStr">
+      <c r="E149" s="86" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="15" customHeight="1" s="50">
-      <c r="A148" s="49" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="49" t="inlineStr">
         <is>
           <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
         </is>
       </c>
-      <c r="B148" s="49" t="inlineStr">
+      <c r="B150" s="49" t="inlineStr">
         <is>
           <t>All international</t>
         </is>
       </c>
-      <c r="C148" s="49" t="n">
+      <c r="C150" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D148" s="49" t="inlineStr">
+      <c r="D150" s="49" t="inlineStr">
         <is>
           <t>fedex.com/en-nz</t>
         </is>
       </c>
-      <c r="E148" s="69" t="inlineStr">
+      <c r="E150" s="69" t="inlineStr">
         <is>
           <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1" s="50"/>
-    <row r="150">
-      <c r="A150" s="87" t="inlineStr">
+    <row r="151" ht="15" customHeight="1" s="50"/>
+    <row r="152">
+      <c r="A152" s="87" t="inlineStr">
         <is>
           <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" s="50"/>
-    <row r="152"/>
-    <row r="153" ht="15" customHeight="1" s="50">
-      <c r="A153" s="49" t="inlineStr">
+    <row r="153" ht="15" customHeight="1" s="50"/>
+    <row r="154" ht="15" customHeight="1" s="50"/>
+    <row r="155" ht="15" customHeight="1" s="50">
+      <c r="A155" s="49" t="inlineStr">
         <is>
           <t>Table 6: Public Holidays</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1" s="50">
-      <c r="A154" s="49" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="49" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B154" s="49" t="inlineStr">
+      <c r="B156" s="49" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" s="50">
-      <c r="A155" s="77" t="n">
+    <row r="157" ht="15" customHeight="1" s="50">
+      <c r="A157" s="77" t="n">
         <v>46213</v>
       </c>
-      <c r="B155" s="49" t="inlineStr">
+      <c r="B157" s="49" t="inlineStr">
         <is>
           <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="83" t="n"/>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="50"/>
     <row r="158">
-      <c r="A158" s="49" t="inlineStr">
-        <is>
-          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
-        </is>
-      </c>
+      <c r="A158" s="83" t="n"/>
     </row>
     <row r="159"/>
     <row r="160">
       <c r="A160" s="49" t="inlineStr">
         <is>
+          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" s="49" t="inlineStr">
+        <is>
           <t>Table 7: Operational Exceptions (Non-Business Days)</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="49" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="49" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B161" s="49" t="inlineStr">
+      <c r="B163" s="49" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="83" t="n">
+    <row r="164">
+      <c r="A164" s="83" t="n">
         <v>46244</v>
       </c>
-      <c r="B162" s="49" t="inlineStr">
+      <c r="B164" s="49" t="inlineStr">
         <is>
           <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
         </is>
       </c>
     </row>
-    <row r="163"/>
-    <row r="164">
-      <c r="A164" s="49" t="inlineStr">
+    <row r="165"/>
+    <row r="166">
+      <c r="A166" s="49" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>
@@ -21315,255 +21382,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CB702797C59B384BA5825BD7F91C8FA6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed5aae9864b7dcbba9993313f29ed662">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e670929-1bdc-480c-8510-e43a2a862a6e" xmlns:ns3="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a292da2c54c23b9d44e0544df2ef32" ns2:_="" ns3:_="">
-    <xsd:import namespace="7e670929-1bdc-480c-8510-e43a2a862a6e"/>
-    <xsd:import namespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:Access" minOccurs="0"/>
-                <xsd:element ref="ns2:Access_x002f_Info" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e670929-1bdc-480c-8510-e43a2a862a6e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b25c28e6-01a0-48d2-b828-62504f505dd7" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Access" ma:index="18" nillable="true" ma:displayName="Access" ma:description="Who gets access&#10;" ma:format="Dropdown" ma:internalName="Access">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Access_x002f_Info" ma:index="19" nillable="true" ma:displayName="Access/ Info " ma:format="Dropdown" ma:internalName="Access_x002f_Info">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{156fa16d-c7d6-4694-aac4-2bac9e86d8b0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Access xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" xsi:nil="true"/>
-    <Access_x002f_Info xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8730F84-7464-4849-90AB-B36BBCDFBB37}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BCBBCC7-DE01-451F-B0A7-BDE4A87F5CBF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DCE1B64-365D-4CC1-891C-2A5A901FFC32}"/>
 </file>
--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -17808,7 +17808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="49" min="1" max="2"/>
@@ -20711,53 +20711,62 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="84" t="inlineStr">
+      <c r="A121" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B121" s="49" t="inlineStr">
+        <is>
+          <t>Flo &amp; Frankie</t>
+        </is>
+      </c>
+      <c r="C121" s="49" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D121" s="49" t="n"/>
+      <c r="E121" s="49" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F121" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G121" s="49" t="inlineStr">
+        <is>
+          <t>Customer agreement: Flo &amp; Frankie Order Cut Off orders count as met going forward, per agreement with the customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="84" t="inlineStr">
         <is>
           <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
         </is>
       </c>
     </row>
-    <row r="122"/>
-    <row r="123">
-      <c r="A123" s="81" t="inlineStr">
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" s="81" t="inlineStr">
         <is>
           <t>Order Content-Based Overrides</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="82" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="82" t="inlineStr">
         <is>
           <t>Customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="49" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B125" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C125" s="49" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D125" s="49" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
         </is>
       </c>
     </row>
     <row r="126" ht="126.85" customHeight="1" s="50">
       <c r="A126" s="49" t="inlineStr">
         <is>
-          <t>Simply Clean</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="B126" s="49" t="inlineStr">
@@ -20767,7 +20776,7 @@
       </c>
       <c r="C126" s="49" t="inlineStr">
         <is>
-          <t>briscoes</t>
+          <t>farmers</t>
         </is>
       </c>
       <c r="D126" s="49" t="inlineStr">
@@ -20779,7 +20788,7 @@
     <row r="127">
       <c r="A127" s="49" t="inlineStr">
         <is>
-          <t>Vixxen</t>
+          <t>Simply Clean</t>
         </is>
       </c>
       <c r="B127" s="49" t="inlineStr">
@@ -20789,137 +20798,132 @@
       </c>
       <c r="C127" s="49" t="inlineStr">
         <is>
-          <t>farmers</t>
+          <t>briscoes</t>
         </is>
       </c>
       <c r="D127" s="49" t="inlineStr">
         <is>
-          <t>Next Monday (20:00)</t>
-        </is>
-      </c>
-      <c r="E127" s="83" t="n">
-        <v>46251</v>
-      </c>
-      <c r="F127" s="83" t="n">
-        <v>46254</v>
+          <t>Next Tuesday (17:00)</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="49" t="inlineStr">
         <is>
-          <t>Gym Equip</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="B128" s="49" t="inlineStr">
         <is>
-          <t>All Orders</t>
+          <t>Delivery Company Name</t>
         </is>
       </c>
       <c r="C128" s="49" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>farmers</t>
         </is>
       </c>
       <c r="D128" s="49" t="inlineStr">
         <is>
-          <t>Fixed (2026-09-02 20:00)</t>
-        </is>
-      </c>
-      <c r="E128" s="83" t="n"/>
+          <t>Next Monday (20:00)</t>
+        </is>
+      </c>
+      <c r="E128" s="83" t="n">
+        <v>46251</v>
+      </c>
       <c r="F128" s="83" t="n">
-        <v>46266</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="50">
       <c r="A129" s="49" t="inlineStr">
         <is>
+          <t>Gym Equip</t>
+        </is>
+      </c>
+      <c r="B129" s="49" t="inlineStr">
+        <is>
+          <t>All Orders</t>
+        </is>
+      </c>
+      <c r="C129" s="49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D129" s="49" t="inlineStr">
+        <is>
+          <t>Fixed (2026-09-02 20:00)</t>
+        </is>
+      </c>
+      <c r="E129" s="83" t="n"/>
+      <c r="F129" s="83" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="50">
+      <c r="A130" s="49" t="inlineStr">
+        <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="B129" s="49" t="inlineStr">
+      <c r="B130" s="49" t="inlineStr">
         <is>
           <t>Delivery Company Name</t>
         </is>
       </c>
-      <c r="C129" s="49" t="inlineStr">
+      <c r="C130" s="49" t="inlineStr">
         <is>
           <t>briscoes group</t>
         </is>
       </c>
-      <c r="D129" s="49" t="inlineStr">
+      <c r="D130" s="49" t="inlineStr">
         <is>
           <t>Fixed (2026-09-18 20:00)</t>
         </is>
       </c>
-      <c r="E129" s="83" t="n">
+      <c r="E130" s="83" t="n">
         <v>46280</v>
       </c>
-      <c r="F129" s="83" t="n">
+      <c r="F130" s="83" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" s="50"/>
     <row r="131" ht="23.85" customHeight="1" s="50"/>
     <row r="132" ht="15" customHeight="1" s="50"/>
     <row r="133" ht="23.85" customHeight="1" s="50"/>
     <row r="134" ht="23.85" customHeight="1" s="50"/>
-    <row r="135">
-      <c r="A135" s="84" t="inlineStr">
+    <row r="135"/>
+    <row r="136" ht="99.95" customHeight="1" s="50">
+      <c r="A136" s="84" t="inlineStr">
         <is>
           <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="99.95" customHeight="1" s="50"/>
     <row r="137"/>
-    <row r="138">
-      <c r="A138" s="85" t="inlineStr">
+    <row r="138"/>
+    <row r="139" ht="15" customHeight="1" s="50">
+      <c r="A139" s="85" t="inlineStr">
         <is>
           <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1" s="50">
-      <c r="A139" s="86" t="inlineStr">
+    <row r="140" ht="15" customHeight="1" s="50">
+      <c r="A140" s="86" t="inlineStr">
         <is>
           <t>Match Field</t>
         </is>
       </c>
-      <c r="F139" s="86" t="inlineStr">
+      <c r="F140" s="86" t="inlineStr">
         <is>
           <t>Attribute To</t>
         </is>
       </c>
-      <c r="G139" s="86" t="inlineStr">
+      <c r="G140" s="86" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="15" customHeight="1" s="50">
-      <c r="A140" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B140" s="49" t="inlineStr">
-        <is>
-          <t>supercheap</t>
-        </is>
-      </c>
-      <c r="C140" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F140" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G140" s="69" t="inlineStr">
-        <is>
-          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
         </is>
       </c>
     </row>
@@ -20929,6 +20933,26 @@
           <t>ShipTo</t>
         </is>
       </c>
+      <c r="B141" s="49" t="inlineStr">
+        <is>
+          <t>supercheap</t>
+        </is>
+      </c>
+      <c r="C141" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F141" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G141" s="69" t="inlineStr">
+        <is>
+          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="49" t="inlineStr">
@@ -20936,26 +20960,6 @@
           <t>ShipTo</t>
         </is>
       </c>
-      <c r="B142" s="49" t="inlineStr">
-        <is>
-          <t>srg</t>
-        </is>
-      </c>
-      <c r="C142" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F142" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G142" s="69" t="inlineStr">
-        <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
     </row>
     <row r="143" ht="46.25" customHeight="1" s="50">
       <c r="A143" s="49" t="inlineStr">
@@ -20965,177 +20969,204 @@
       </c>
       <c r="B143" s="49" t="inlineStr">
         <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C143" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F143" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G143" s="69" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B144" s="49" t="inlineStr">
+        <is>
           <t>repco</t>
         </is>
       </c>
-      <c r="C143" s="49" t="inlineStr">
+      <c r="C144" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="F143" s="49" t="inlineStr">
+      <c r="F144" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="G143" s="69" t="inlineStr">
+      <c r="G144" s="69" t="inlineStr">
         <is>
           <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
-    <row r="144"/>
-    <row r="145">
-      <c r="A145" s="87" t="inlineStr">
+    <row r="145"/>
+    <row r="146" ht="15" customHeight="1" s="50">
+      <c r="A146" s="87" t="inlineStr">
         <is>
           <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="15" customHeight="1" s="50"/>
     <row r="147" ht="15" customHeight="1" s="50"/>
-    <row r="148" ht="15" customHeight="1" s="50">
-      <c r="A148" s="85" t="inlineStr">
+    <row r="148" ht="15" customHeight="1" s="50"/>
+    <row r="149" ht="15" customHeight="1" s="50">
+      <c r="A149" s="85" t="inlineStr">
         <is>
           <t>Table 5: International Carrier SLAs</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1" s="50">
-      <c r="A149" s="86" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="86" t="inlineStr">
         <is>
           <t>Service Code</t>
         </is>
       </c>
-      <c r="B149" s="86" t="inlineStr">
+      <c r="B150" s="86" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="C149" s="86" t="inlineStr">
+      <c r="C150" s="86" t="inlineStr">
         <is>
           <t>Business Days</t>
         </is>
       </c>
-      <c r="D149" s="86" t="inlineStr">
+      <c r="D150" s="86" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E149" s="86" t="inlineStr">
+      <c r="E150" s="86" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="49" t="inlineStr">
+    <row r="151" ht="15" customHeight="1" s="50">
+      <c r="A151" s="49" t="inlineStr">
         <is>
           <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
         </is>
       </c>
-      <c r="B150" s="49" t="inlineStr">
+      <c r="B151" s="49" t="inlineStr">
         <is>
           <t>All international</t>
         </is>
       </c>
-      <c r="C150" s="49" t="n">
+      <c r="C151" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D150" s="49" t="inlineStr">
+      <c r="D151" s="49" t="inlineStr">
         <is>
           <t>fedex.com/en-nz</t>
         </is>
       </c>
-      <c r="E150" s="69" t="inlineStr">
+      <c r="E151" s="69" t="inlineStr">
         <is>
           <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" s="50"/>
-    <row r="152">
-      <c r="A152" s="87" t="inlineStr">
+    <row r="152"/>
+    <row r="153" ht="15" customHeight="1" s="50">
+      <c r="A153" s="87" t="inlineStr">
         <is>
           <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="15" customHeight="1" s="50"/>
     <row r="154" ht="15" customHeight="1" s="50"/>
-    <row r="155" ht="15" customHeight="1" s="50">
-      <c r="A155" s="49" t="inlineStr">
-        <is>
-          <t>Table 6: Public Holidays</t>
-        </is>
-      </c>
-    </row>
+    <row r="155" ht="15" customHeight="1" s="50"/>
     <row r="156">
       <c r="A156" s="49" t="inlineStr">
         <is>
+          <t>Table 6: Public Holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="50">
+      <c r="A157" s="49" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B156" s="49" t="inlineStr">
+      <c r="B157" s="49" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1" s="50">
-      <c r="A157" s="77" t="n">
+    <row r="158">
+      <c r="A158" s="77" t="n">
         <v>46213</v>
       </c>
-      <c r="B157" s="49" t="inlineStr">
+      <c r="B158" s="49" t="inlineStr">
         <is>
           <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="83" t="n"/>
-    </row>
-    <row r="159"/>
-    <row r="160">
-      <c r="A160" s="49" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="83" t="n"/>
+    </row>
+    <row r="160"/>
+    <row r="161">
+      <c r="A161" s="49" t="inlineStr">
         <is>
           <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
         </is>
       </c>
     </row>
-    <row r="161"/>
-    <row r="162">
-      <c r="A162" s="49" t="inlineStr">
-        <is>
-          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
-        </is>
-      </c>
-    </row>
+    <row r="162"/>
     <row r="163">
       <c r="A163" s="49" t="inlineStr">
         <is>
+          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="49" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B163" s="49" t="inlineStr">
+      <c r="B164" s="49" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="83" t="n">
+    <row r="165">
+      <c r="A165" s="83" t="n">
         <v>46244</v>
       </c>
-      <c r="B164" s="49" t="inlineStr">
+      <c r="B165" s="49" t="inlineStr">
         <is>
           <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
         </is>
       </c>
     </row>
-    <row r="165"/>
-    <row r="166">
-      <c r="A166" s="49" t="inlineStr">
+    <row r="166"/>
+    <row r="167">
+      <c r="A167" s="49" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>

--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -292,7 +292,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -558,6 +558,7 @@
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17808,7 +17809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="49" min="1" max="2"/>
@@ -20641,148 +20642,123 @@
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="50">
-      <c r="A119" s="90" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B119" s="49" t="inlineStr">
-        <is>
-          <t>Salt Shark</t>
-        </is>
-      </c>
-      <c r="C119" s="49" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="D119" s="49" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E119" s="49" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F119" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G119" s="49" t="inlineStr">
-        <is>
-          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) — extension approved, not a genuine cutoff miss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" s="50">
-      <c r="A120" s="90" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B120" s="49" t="inlineStr">
-        <is>
-          <t>Salt Shark</t>
-        </is>
-      </c>
-      <c r="C120" s="49" t="inlineStr">
-        <is>
-          <t>4953</t>
-        </is>
-      </c>
-      <c r="D120" s="49" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E120" s="49" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F120" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G120" s="49" t="inlineStr">
-        <is>
-          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) — extension approved, not a genuine cutoff miss.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A119" s="84" t="inlineStr">
+        <is>
+          <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="50"/>
     <row r="121">
-      <c r="A121" s="90" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B121" s="49" t="inlineStr">
-        <is>
-          <t>Flo &amp; Frankie</t>
-        </is>
-      </c>
-      <c r="C121" s="49" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="D121" s="49" t="n"/>
-      <c r="E121" s="49" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F121" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G121" s="49" t="inlineStr">
-        <is>
-          <t>Customer agreement: Flo &amp; Frankie Order Cut Off orders count as met going forward, per agreement with the customer.</t>
+      <c r="A121" s="81" t="inlineStr">
+        <is>
+          <t>Order Content-Based Overrides</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="84" t="inlineStr">
-        <is>
-          <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123"/>
+      <c r="A122" s="82" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="49" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B123" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C123" s="49" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D123" s="49" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
+        </is>
+      </c>
+    </row>
     <row r="124">
-      <c r="A124" s="81" t="inlineStr">
-        <is>
-          <t>Order Content-Based Overrides</t>
+      <c r="A124" s="49" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="B124" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C124" s="49" t="inlineStr">
+        <is>
+          <t>briscoes</t>
+        </is>
+      </c>
+      <c r="D124" s="49" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="82" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
+      <c r="A125" s="49" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B125" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C125" s="49" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D125" s="49" t="inlineStr">
+        <is>
+          <t>Next Monday (20:00)</t>
+        </is>
+      </c>
+      <c r="E125" s="83" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F125" s="83" t="n">
+        <v>46254</v>
       </c>
     </row>
     <row r="126" ht="126.85" customHeight="1" s="50">
       <c r="A126" s="49" t="inlineStr">
         <is>
-          <t>Vixxen</t>
+          <t>Gym Equip</t>
         </is>
       </c>
       <c r="B126" s="49" t="inlineStr">
         <is>
-          <t>Delivery Company Name</t>
+          <t>All Orders</t>
         </is>
       </c>
       <c r="C126" s="49" t="inlineStr">
         <is>
-          <t>farmers</t>
+          <t>all</t>
         </is>
       </c>
       <c r="D126" s="49" t="inlineStr">
         <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
+          <t>Fixed (2026-09-02 20:00)</t>
+        </is>
+      </c>
+      <c r="E126" s="83" t="n"/>
+      <c r="F126" s="83" t="n">
+        <v>46266</v>
       </c>
     </row>
     <row r="127">
@@ -20798,132 +20774,115 @@
       </c>
       <c r="C127" s="49" t="inlineStr">
         <is>
-          <t>briscoes</t>
+          <t>briscoes group</t>
         </is>
       </c>
       <c r="D127" s="49" t="inlineStr">
         <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="49" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B128" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C128" s="49" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D128" s="49" t="inlineStr">
-        <is>
-          <t>Next Monday (20:00)</t>
-        </is>
-      </c>
-      <c r="E128" s="83" t="n">
-        <v>46251</v>
-      </c>
-      <c r="F128" s="83" t="n">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="129" ht="15" customHeight="1" s="50">
-      <c r="A129" s="49" t="inlineStr">
-        <is>
-          <t>Gym Equip</t>
-        </is>
-      </c>
-      <c r="B129" s="49" t="inlineStr">
-        <is>
-          <t>All Orders</t>
-        </is>
-      </c>
-      <c r="C129" s="49" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D129" s="49" t="inlineStr">
-        <is>
-          <t>Fixed (2026-09-02 20:00)</t>
-        </is>
-      </c>
-      <c r="E129" s="83" t="n"/>
-      <c r="F129" s="83" t="n">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="50">
-      <c r="A130" s="49" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="B130" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C130" s="49" t="inlineStr">
-        <is>
-          <t>briscoes group</t>
-        </is>
-      </c>
-      <c r="D130" s="49" t="inlineStr">
-        <is>
           <t>Fixed (2026-09-18 20:00)</t>
         </is>
       </c>
-      <c r="E130" s="83" t="n">
+      <c r="E127" s="83" t="n">
         <v>46280</v>
       </c>
-      <c r="F130" s="83" t="n">
+      <c r="F127" s="83" t="n">
         <v>46280</v>
       </c>
     </row>
+    <row r="129" ht="15" customHeight="1" s="50"/>
+    <row r="130" ht="15" customHeight="1" s="50"/>
     <row r="131" ht="23.85" customHeight="1" s="50"/>
     <row r="132" ht="15" customHeight="1" s="50"/>
-    <row r="133" ht="23.85" customHeight="1" s="50"/>
+    <row r="133" ht="23.85" customHeight="1" s="50">
+      <c r="A133" s="84" t="inlineStr">
+        <is>
+          <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="23.85" customHeight="1" s="50"/>
-    <row r="135"/>
     <row r="136" ht="99.95" customHeight="1" s="50">
-      <c r="A136" s="84" t="inlineStr">
-        <is>
-          <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137"/>
-    <row r="138"/>
+      <c r="A136" s="85" t="inlineStr">
+        <is>
+          <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="86" t="inlineStr">
+        <is>
+          <t>Match Field</t>
+        </is>
+      </c>
+      <c r="F137" s="86" t="inlineStr">
+        <is>
+          <t>Attribute To</t>
+        </is>
+      </c>
+      <c r="G137" s="86" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B138" s="49" t="inlineStr">
+        <is>
+          <t>supercheap</t>
+        </is>
+      </c>
+      <c r="C138" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F138" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G138" s="69" t="inlineStr">
+        <is>
+          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
+        </is>
+      </c>
+    </row>
     <row r="139" ht="15" customHeight="1" s="50">
-      <c r="A139" s="85" t="inlineStr">
-        <is>
-          <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
+      <c r="A139" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="50">
-      <c r="A140" s="86" t="inlineStr">
-        <is>
-          <t>Match Field</t>
-        </is>
-      </c>
-      <c r="F140" s="86" t="inlineStr">
-        <is>
-          <t>Attribute To</t>
-        </is>
-      </c>
-      <c r="G140" s="86" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="A140" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B140" s="49" t="inlineStr">
+        <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C140" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F140" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G140" s="69" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20894,7 @@
       </c>
       <c r="B141" s="49" t="inlineStr">
         <is>
-          <t>supercheap</t>
+          <t>repco</t>
         </is>
       </c>
       <c r="C141" s="49" t="inlineStr">
@@ -20950,223 +20909,156 @@
       </c>
       <c r="G141" s="69" t="inlineStr">
         <is>
-          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
+          <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
     <row r="143" ht="46.25" customHeight="1" s="50">
-      <c r="A143" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B143" s="49" t="inlineStr">
-        <is>
-          <t>srg</t>
-        </is>
-      </c>
-      <c r="C143" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F143" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G143" s="69" t="inlineStr">
-        <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B144" s="49" t="inlineStr">
-        <is>
-          <t>repco</t>
-        </is>
-      </c>
-      <c r="C144" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F144" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G144" s="69" t="inlineStr">
-        <is>
-          <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="145"/>
+      <c r="A143" s="87" t="inlineStr">
+        <is>
+          <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
+        </is>
+      </c>
+    </row>
     <row r="146" ht="15" customHeight="1" s="50">
-      <c r="A146" s="87" t="inlineStr">
-        <is>
-          <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="15" customHeight="1" s="50"/>
-    <row r="148" ht="15" customHeight="1" s="50"/>
-    <row r="149" ht="15" customHeight="1" s="50">
-      <c r="A149" s="85" t="inlineStr">
+      <c r="A146" s="85" t="inlineStr">
         <is>
           <t>Table 5: International Carrier SLAs</t>
         </is>
       </c>
     </row>
+    <row r="147" ht="15" customHeight="1" s="50">
+      <c r="A147" s="86" t="inlineStr">
+        <is>
+          <t>Service Code</t>
+        </is>
+      </c>
+      <c r="B147" s="86" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="C147" s="86" t="inlineStr">
+        <is>
+          <t>Business Days</t>
+        </is>
+      </c>
+      <c r="D147" s="86" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E147" s="86" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="50">
+      <c r="A148" s="49" t="inlineStr">
+        <is>
+          <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
+        </is>
+      </c>
+      <c r="B148" s="49" t="inlineStr">
+        <is>
+          <t>All international</t>
+        </is>
+      </c>
+      <c r="C148" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" s="49" t="inlineStr">
+        <is>
+          <t>fedex.com/en-nz</t>
+        </is>
+      </c>
+      <c r="E148" s="69" t="inlineStr">
+        <is>
+          <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="50"/>
     <row r="150">
-      <c r="A150" s="86" t="inlineStr">
-        <is>
-          <t>Service Code</t>
-        </is>
-      </c>
-      <c r="B150" s="86" t="inlineStr">
-        <is>
-          <t>Destination</t>
-        </is>
-      </c>
-      <c r="C150" s="86" t="inlineStr">
-        <is>
-          <t>Business Days</t>
-        </is>
-      </c>
-      <c r="D150" s="86" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E150" s="86" t="inlineStr">
+      <c r="A150" s="87" t="inlineStr">
+        <is>
+          <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1" s="50"/>
+    <row r="153" ht="15" customHeight="1" s="50">
+      <c r="A153" s="49" t="inlineStr">
+        <is>
+          <t>Table 6: Public Holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1" s="50">
+      <c r="A154" s="49" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B154" s="49" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" s="50">
-      <c r="A151" s="49" t="inlineStr">
-        <is>
-          <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
-        </is>
-      </c>
-      <c r="B151" s="49" t="inlineStr">
-        <is>
-          <t>All international</t>
-        </is>
-      </c>
-      <c r="C151" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D151" s="49" t="inlineStr">
-        <is>
-          <t>fedex.com/en-nz</t>
-        </is>
-      </c>
-      <c r="E151" s="69" t="inlineStr">
-        <is>
-          <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="152"/>
-    <row r="153" ht="15" customHeight="1" s="50">
-      <c r="A153" s="87" t="inlineStr">
-        <is>
-          <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="15" customHeight="1" s="50"/>
-    <row r="155" ht="15" customHeight="1" s="50"/>
+    <row r="155" ht="15" customHeight="1" s="50">
+      <c r="A155" s="77" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B155" s="49" t="inlineStr">
+        <is>
+          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
+        </is>
+      </c>
+    </row>
     <row r="156">
-      <c r="A156" s="49" t="inlineStr">
-        <is>
-          <t>Table 6: Public Holidays</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="50">
-      <c r="A157" s="49" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B157" s="49" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
+      <c r="A156" s="83" t="n"/>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="50"/>
     <row r="158">
-      <c r="A158" s="77" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B158" s="49" t="inlineStr">
-        <is>
-          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="83" t="n"/>
-    </row>
-    <row r="160"/>
+      <c r="A158" s="49" t="inlineStr">
+        <is>
+          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="49" t="inlineStr">
+        <is>
+          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+        </is>
+      </c>
+    </row>
     <row r="161">
       <c r="A161" s="49" t="inlineStr">
         <is>
-          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162"/>
-    <row r="163">
-      <c r="A163" s="49" t="inlineStr">
-        <is>
-          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B161" s="49" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="83" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B162" s="49" t="inlineStr">
+        <is>
+          <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="49" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B164" s="49" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="83" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B165" s="49" t="inlineStr">
-        <is>
-          <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
-        </is>
-      </c>
-    </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="49" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>
@@ -21193,7 +21085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="49" min="1" max="1"/>
@@ -21405,6 +21297,52 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="91" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cross-labelled shipping labels - items picked accurately but shipped to wrong destination due to label mix-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cross-labelled shipping labels - items picked accurately but shipped to wrong destination due to label mix-up</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -21413,4 +21351,255 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CB702797C59B384BA5825BD7F91C8FA6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed5aae9864b7dcbba9993313f29ed662">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e670929-1bdc-480c-8510-e43a2a862a6e" xmlns:ns3="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a292da2c54c23b9d44e0544df2ef32" ns2:_="" ns3:_="">
+    <xsd:import namespace="7e670929-1bdc-480c-8510-e43a2a862a6e"/>
+    <xsd:import namespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:Access" minOccurs="0"/>
+                <xsd:element ref="ns2:Access_x002f_Info" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e670929-1bdc-480c-8510-e43a2a862a6e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b25c28e6-01a0-48d2-b828-62504f505dd7" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Access" ma:index="18" nillable="true" ma:displayName="Access" ma:description="Who gets access&#10;" ma:format="Dropdown" ma:internalName="Access">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Access_x002f_Info" ma:index="19" nillable="true" ma:displayName="Access/ Info " ma:format="Dropdown" ma:internalName="Access_x002f_Info">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{156fa16d-c7d6-4694-aac4-2bac9e86d8b0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Access xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" xsi:nil="true"/>
+    <Access_x002f_Info xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{945D8665-BB08-45C8-840D-18D1435796C1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BD9ABE0-6CF6-4F1E-898D-882E0269A924}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B5FEB4-9DED-4683-B971-45C8DEFC8855}"/>
 </file>
--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Schedule" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_Data" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issue Log" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_Calc" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Charts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KPI Schedule" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Customers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="KPI_Data" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Exceptions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Issue Log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Dashboard_Calc" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'KPI_Data'!$A$3:$J$295</definedName>
@@ -292,7 +292,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -559,6 +559,9 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,14 +698,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -724,8 +727,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -750,10 +753,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A7EBB"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
@@ -764,16 +767,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -902,10 +905,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BE4B48"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="BE4B48"/>
               </a:solidFill>
@@ -916,16 +919,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1020,7 +1023,7 @@
         </ser>
         <hiLowLines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1042,7 +1045,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -1051,9 +1054,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -1084,7 +1087,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -1096,9 +1099,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1300" b="0" strike="noStrike">
                     <a:uFillTx/>
@@ -1120,8 +1123,8 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:noFill/>
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1132,7 +1135,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -1141,9 +1144,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -1167,16 +1170,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1196,10 +1199,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1211,14 +1214,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1240,8 +1243,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1266,10 +1269,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A7EBB"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
@@ -1280,16 +1283,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1418,10 +1421,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BE4B48"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="BE4B48"/>
               </a:solidFill>
@@ -1432,16 +1435,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1521,7 +1524,7 @@
         </ser>
         <hiLowLines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1543,7 +1546,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -1552,9 +1555,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -1585,7 +1588,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -1597,9 +1600,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1300" b="0" strike="noStrike">
                     <a:uFillTx/>
@@ -1621,8 +1624,8 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:noFill/>
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1633,7 +1636,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -1642,9 +1645,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -1668,16 +1671,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1697,10 +1700,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1712,14 +1715,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1741,8 +1744,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1767,10 +1770,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A7EBB"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
@@ -1781,16 +1784,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1919,10 +1922,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BE4B48"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="BE4B48"/>
               </a:solidFill>
@@ -1933,16 +1936,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2040,7 +2043,7 @@
         </ser>
         <hiLowLines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2062,7 +2065,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2071,9 +2074,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2104,7 +2107,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2116,9 +2119,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1300" b="0" strike="noStrike">
                     <a:uFillTx/>
@@ -2140,8 +2143,8 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:noFill/>
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2152,7 +2155,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2161,9 +2164,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2187,16 +2190,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2216,10 +2219,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2231,14 +2234,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2260,8 +2263,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2286,10 +2289,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A7EBB"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
@@ -2300,16 +2303,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2438,10 +2441,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BE4B48"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="BE4B48"/>
               </a:solidFill>
@@ -2452,16 +2455,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2547,7 +2550,7 @@
         </ser>
         <hiLowLines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2569,7 +2572,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2578,9 +2581,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2611,7 +2614,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2623,9 +2626,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1300" b="0" strike="noStrike">
                     <a:uFillTx/>
@@ -2647,8 +2650,8 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:noFill/>
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2659,7 +2662,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2668,9 +2671,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2694,16 +2697,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2723,10 +2726,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2738,14 +2741,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2767,8 +2770,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2793,10 +2796,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A7EBB"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
@@ -2807,16 +2810,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2945,10 +2948,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BE4B48"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="BE4B48"/>
               </a:solidFill>
@@ -2959,16 +2962,16 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -3057,7 +3060,7 @@
         </ser>
         <hiLowLines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3079,7 +3082,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -3088,9 +3091,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -3121,7 +3124,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -3133,9 +3136,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1300" b="0" strike="noStrike">
                     <a:uFillTx/>
@@ -3157,8 +3160,8 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+            <a:noFill/>
+            <a:ln w="0">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3169,7 +3172,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -3178,9 +3181,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -3204,16 +3207,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -3233,10 +3236,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -3248,14 +3251,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -3277,8 +3280,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3304,10 +3307,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
@@ -3318,9 +3321,9 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -3388,10 +3391,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="C0504D"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
@@ -3402,9 +3405,9 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -3468,7 +3471,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -3477,9 +3480,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -3510,7 +3513,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -3524,7 +3527,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -3533,9 +3536,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -3559,16 +3562,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -3588,10 +3591,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -3603,14 +3606,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -3632,8 +3635,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -3659,10 +3662,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
@@ -3673,9 +3676,9 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -3743,10 +3746,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="C0504D"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:solidFill>
                 <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
@@ -3757,9 +3760,9 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -3823,7 +3826,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -3832,9 +3835,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -3865,7 +3868,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -3879,7 +3882,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -3888,9 +3891,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -3914,16 +3917,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -3943,10 +3946,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -3958,7 +3961,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -3978,9 +3981,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4005,9 +4008,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4032,9 +4035,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4059,9 +4062,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4086,9 +4089,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4113,9 +4116,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4140,9 +4143,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4848,6 +4851,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26.25" customHeight="1" s="50">
       <c r="A4" s="89" t="inlineStr">
         <is>
@@ -6199,6 +6203,8 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="50">
       <c r="A19" s="57" t="inlineStr">
         <is>
@@ -6272,6 +6278,8 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="50">
       <c r="A24" s="57" t="inlineStr">
         <is>
@@ -6380,6 +6388,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="57" t="inlineStr">
         <is>
@@ -6403,6 +6412,7 @@
         <v/>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="26.25" customHeight="1" s="50">
       <c r="A7" s="60" t="inlineStr">
         <is>
@@ -6646,6 +6656,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="57" t="inlineStr">
         <is>
@@ -6704,6 +6715,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="48" customHeight="1" s="50">
       <c r="A4" s="68" t="inlineStr">
         <is>
@@ -6776,6 +6788,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="50">
       <c r="A11" s="57" t="inlineStr">
         <is>
@@ -6818,6 +6831,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="50">
       <c r="A18" s="57" t="inlineStr">
         <is>
@@ -6877,6 +6891,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="60" t="inlineStr">
         <is>
@@ -7080,6 +7095,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="50">
       <c r="A3" s="60" t="inlineStr">
         <is>
@@ -7304,6 +7320,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="26.25" customHeight="1" s="50">
       <c r="A3" s="60" t="inlineStr">
         <is>
@@ -17809,7 +17826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="49" min="1" max="2"/>
@@ -17824,6 +17841,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="50">
       <c r="A3" s="81" t="inlineStr">
         <is>
@@ -18034,6 +18052,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="50">
       <c r="A15" s="84" t="inlineStr">
         <is>
@@ -18041,6 +18064,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="50">
       <c r="A17" s="81" t="inlineStr">
         <is>
@@ -18690,6 +18714,10 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="50">
       <c r="A40" s="77" t="n">
         <v>46196</v>
@@ -20642,123 +20670,148 @@
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="50">
-      <c r="A119" s="84" t="inlineStr">
+      <c r="A119" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B119" s="49" t="inlineStr">
+        <is>
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C119" s="92" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="D119" s="92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E119" s="49" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F119" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G119" s="49" t="inlineStr">
+        <is>
+          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) - extension approved, not a genuine cutoff miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="50">
+      <c r="A120" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B120" s="49" t="inlineStr">
+        <is>
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C120" s="92" t="inlineStr">
+        <is>
+          <t>4953</t>
+        </is>
+      </c>
+      <c r="D120" s="92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E120" s="49" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F120" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G120" s="49" t="inlineStr">
+        <is>
+          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) - extension approved, not a genuine cutoff miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1" s="50">
+      <c r="A121" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B121" s="49" t="inlineStr">
+        <is>
+          <t>Flo &amp; Frankie</t>
+        </is>
+      </c>
+      <c r="C121" s="92" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D121" s="92" t="n"/>
+      <c r="E121" s="49" t="inlineStr">
+        <is>
+          <t>Order Cut Off</t>
+        </is>
+      </c>
+      <c r="F121" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="G121" s="49" t="inlineStr">
+        <is>
+          <t>Customer agreement: Flo &amp; Frankie Order Cut Off orders count as met going forward, per agreement with the customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="50">
+      <c r="A122" s="84" t="inlineStr">
         <is>
           <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="50"/>
-    <row r="121">
-      <c r="A121" s="81" t="inlineStr">
+    <row r="123" ht="15" customHeight="1" s="50"/>
+    <row r="124">
+      <c r="A124" s="81" t="inlineStr">
         <is>
           <t>Order Content-Based Overrides</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="82" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="82" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="49" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B123" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C123" s="49" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D123" s="49" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="49" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="B124" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C124" s="49" t="inlineStr">
-        <is>
-          <t>briscoes</t>
-        </is>
-      </c>
-      <c r="D124" s="49" t="inlineStr">
-        <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="49" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B125" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C125" s="49" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D125" s="49" t="inlineStr">
-        <is>
-          <t>Next Monday (20:00)</t>
-        </is>
-      </c>
-      <c r="E125" s="83" t="n">
-        <v>46251</v>
-      </c>
-      <c r="F125" s="83" t="n">
-        <v>46254</v>
       </c>
     </row>
     <row r="126" ht="126.85" customHeight="1" s="50">
       <c r="A126" s="49" t="inlineStr">
         <is>
-          <t>Gym Equip</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="B126" s="49" t="inlineStr">
         <is>
-          <t>All Orders</t>
+          <t>Delivery Company Name</t>
         </is>
       </c>
       <c r="C126" s="49" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>farmers</t>
         </is>
       </c>
       <c r="D126" s="49" t="inlineStr">
         <is>
-          <t>Fixed (2026-09-02 20:00)</t>
-        </is>
-      </c>
-      <c r="E126" s="83" t="n"/>
-      <c r="F126" s="83" t="n">
-        <v>46266</v>
+          <t>Next Tuesday (17:00)</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -20774,115 +20827,159 @@
       </c>
       <c r="C127" s="49" t="inlineStr">
         <is>
+          <t>briscoes</t>
+        </is>
+      </c>
+      <c r="D127" s="49" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="49" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B128" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C128" s="49" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D128" s="49" t="inlineStr">
+        <is>
+          <t>Next Monday (20:00)</t>
+        </is>
+      </c>
+      <c r="E128" s="83" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F128" s="83" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="129" ht="126.85" customHeight="1" s="50">
+      <c r="A129" s="49" t="inlineStr">
+        <is>
+          <t>Gym Equip</t>
+        </is>
+      </c>
+      <c r="B129" s="49" t="inlineStr">
+        <is>
+          <t>All Orders</t>
+        </is>
+      </c>
+      <c r="C129" s="49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D129" s="49" t="inlineStr">
+        <is>
+          <t>Fixed (2026-09-02 20:00)</t>
+        </is>
+      </c>
+      <c r="E129" s="83" t="n"/>
+      <c r="F129" s="83" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="50">
+      <c r="A130" s="49" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="B130" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C130" s="49" t="inlineStr">
+        <is>
           <t>briscoes group</t>
         </is>
       </c>
-      <c r="D127" s="49" t="inlineStr">
+      <c r="D130" s="49" t="inlineStr">
         <is>
           <t>Fixed (2026-09-18 20:00)</t>
         </is>
       </c>
-      <c r="E127" s="83" t="n">
+      <c r="E130" s="83" t="n">
         <v>46280</v>
       </c>
-      <c r="F127" s="83" t="n">
+      <c r="F130" s="83" t="n">
         <v>46280</v>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1" s="50"/>
-    <row r="130" ht="15" customHeight="1" s="50"/>
-    <row r="131" ht="23.85" customHeight="1" s="50"/>
+    <row r="131" ht="23.85" customHeight="1" s="50">
+      <c r="A131" s="49" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B131" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C131" s="49" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D131" s="49" t="inlineStr">
+        <is>
+          <t>Fixed (2026-10-13 20:00)</t>
+        </is>
+      </c>
+      <c r="E131" s="83" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F131" s="83" t="n">
+        <v>46300</v>
+      </c>
+    </row>
     <row r="132" ht="15" customHeight="1" s="50"/>
-    <row r="133" ht="23.85" customHeight="1" s="50">
-      <c r="A133" s="84" t="inlineStr">
+    <row r="133" ht="15" customHeight="1" s="50"/>
+    <row r="134" ht="23.85" customHeight="1" s="50"/>
+    <row r="135" ht="15" customHeight="1" s="50"/>
+    <row r="136" ht="23.85" customHeight="1" s="50">
+      <c r="A136" s="84" t="inlineStr">
         <is>
           <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="23.85" customHeight="1" s="50"/>
-    <row r="136" ht="99.95" customHeight="1" s="50">
-      <c r="A136" s="85" t="inlineStr">
+    <row r="137" ht="23.85" customHeight="1" s="50"/>
+    <row r="138"/>
+    <row r="139" ht="99.95" customHeight="1" s="50">
+      <c r="A139" s="85" t="inlineStr">
         <is>
           <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="86" t="inlineStr">
+    <row r="140" ht="15" customHeight="1" s="50">
+      <c r="A140" s="86" t="inlineStr">
         <is>
           <t>Match Field</t>
         </is>
       </c>
-      <c r="F137" s="86" t="inlineStr">
+      <c r="F140" s="86" t="inlineStr">
         <is>
           <t>Attribute To</t>
         </is>
       </c>
-      <c r="G137" s="86" t="inlineStr">
+      <c r="G140" s="86" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B138" s="49" t="inlineStr">
-        <is>
-          <t>supercheap</t>
-        </is>
-      </c>
-      <c r="C138" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F138" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G138" s="69" t="inlineStr">
-        <is>
-          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="50">
-      <c r="A139" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="15" customHeight="1" s="50">
-      <c r="A140" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B140" s="49" t="inlineStr">
-        <is>
-          <t>srg</t>
-        </is>
-      </c>
-      <c r="C140" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F140" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G140" s="69" t="inlineStr">
-        <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
@@ -20894,171 +20991,238 @@
       </c>
       <c r="B141" s="49" t="inlineStr">
         <is>
+          <t>supercheap</t>
+        </is>
+      </c>
+      <c r="C141" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F141" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G141" s="69" t="inlineStr">
+        <is>
+          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="50">
+      <c r="A142" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="50">
+      <c r="A143" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B143" s="49" t="inlineStr">
+        <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C143" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F143" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G143" s="69" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="68.65000000000001" customHeight="1" s="50">
+      <c r="A144" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B144" s="49" t="inlineStr">
+        <is>
           <t>repco</t>
         </is>
       </c>
-      <c r="C141" s="49" t="inlineStr">
+      <c r="C144" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="F141" s="49" t="inlineStr">
+      <c r="F144" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="G141" s="69" t="inlineStr">
+      <c r="G144" s="69" t="inlineStr">
         <is>
           <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="46.25" customHeight="1" s="50">
-      <c r="A143" s="87" t="inlineStr">
+    <row r="145"/>
+    <row r="146" ht="46.25" customHeight="1" s="50">
+      <c r="A146" s="87" t="inlineStr">
         <is>
           <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="15" customHeight="1" s="50">
-      <c r="A146" s="85" t="inlineStr">
+    <row r="147" ht="15" customHeight="1" s="50"/>
+    <row r="148" ht="15" customHeight="1" s="50"/>
+    <row r="149" ht="15" customHeight="1" s="50">
+      <c r="A149" s="85" t="inlineStr">
         <is>
           <t>Table 5: International Carrier SLAs</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1" s="50">
-      <c r="A147" s="86" t="inlineStr">
+    <row r="150" ht="15" customHeight="1" s="50">
+      <c r="A150" s="86" t="inlineStr">
         <is>
           <t>Service Code</t>
         </is>
       </c>
-      <c r="B147" s="86" t="inlineStr">
+      <c r="B150" s="86" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="C147" s="86" t="inlineStr">
+      <c r="C150" s="86" t="inlineStr">
         <is>
           <t>Business Days</t>
         </is>
       </c>
-      <c r="D147" s="86" t="inlineStr">
+      <c r="D150" s="86" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E147" s="86" t="inlineStr">
+      <c r="E150" s="86" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="15" customHeight="1" s="50">
-      <c r="A148" s="49" t="inlineStr">
+    <row r="151" ht="15" customHeight="1" s="50">
+      <c r="A151" s="49" t="inlineStr">
         <is>
           <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
         </is>
       </c>
-      <c r="B148" s="49" t="inlineStr">
+      <c r="B151" s="49" t="inlineStr">
         <is>
           <t>All international</t>
         </is>
       </c>
-      <c r="C148" s="49" t="n">
+      <c r="C151" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D148" s="49" t="inlineStr">
+      <c r="D151" s="49" t="inlineStr">
         <is>
           <t>fedex.com/en-nz</t>
         </is>
       </c>
-      <c r="E148" s="69" t="inlineStr">
+      <c r="E151" s="69" t="inlineStr">
         <is>
           <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1" s="50"/>
-    <row r="150">
-      <c r="A150" s="87" t="inlineStr">
+    <row r="152" ht="15" customHeight="1" s="50"/>
+    <row r="153" ht="15" customHeight="1" s="50">
+      <c r="A153" s="87" t="inlineStr">
         <is>
           <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" s="50"/>
-    <row r="153" ht="15" customHeight="1" s="50">
-      <c r="A153" s="49" t="inlineStr">
+    <row r="154" ht="15" customHeight="1" s="50"/>
+    <row r="155" ht="15" customHeight="1" s="50"/>
+    <row r="156" ht="15" customHeight="1" s="50">
+      <c r="A156" s="49" t="inlineStr">
         <is>
           <t>Table 6: Public Holidays</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1" s="50">
-      <c r="A154" s="49" t="inlineStr">
+    <row r="157" ht="15" customHeight="1" s="50">
+      <c r="A157" s="49" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B154" s="49" t="inlineStr">
+      <c r="B157" s="49" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" s="50">
-      <c r="A155" s="77" t="n">
+    <row r="158" ht="15" customHeight="1" s="50">
+      <c r="A158" s="77" t="n">
         <v>46213</v>
       </c>
-      <c r="B155" s="49" t="inlineStr">
+      <c r="B158" s="49" t="inlineStr">
         <is>
           <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="83" t="n"/>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="50"/>
-    <row r="158">
-      <c r="A158" s="49" t="inlineStr">
-        <is>
-          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="49" t="inlineStr">
-        <is>
-          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
-        </is>
-      </c>
-    </row>
+    <row r="159">
+      <c r="A159" s="83" t="n"/>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="50"/>
     <row r="161">
       <c r="A161" s="49" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B161" s="49" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="83" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B162" s="49" t="inlineStr">
-        <is>
-          <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
+          <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162"/>
+    <row r="163">
+      <c r="A163" s="49" t="inlineStr">
+        <is>
+          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="49" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B164" s="49" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="83" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B165" s="49" t="inlineStr">
+        <is>
+          <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166"/>
+    <row r="167">
+      <c r="A167" s="49" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>
@@ -21109,6 +21273,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="82" t="inlineStr">
         <is>
@@ -21301,20 +21466,20 @@
       <c r="A12" s="91" t="n">
         <v>46295</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>3380</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>Cross-labelled shipping labels - items picked accurately but shipped to wrong destination due to label mix-up</t>
         </is>
@@ -21324,20 +21489,20 @@
       <c r="A13" s="91" t="n">
         <v>46295</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>3378</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>Cross-labelled shipping labels - items picked accurately but shipped to wrong destination due to label mix-up</t>
         </is>
@@ -21351,255 +21516,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CB702797C59B384BA5825BD7F91C8FA6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed5aae9864b7dcbba9993313f29ed662">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e670929-1bdc-480c-8510-e43a2a862a6e" xmlns:ns3="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59a292da2c54c23b9d44e0544df2ef32" ns2:_="" ns3:_="">
-    <xsd:import namespace="7e670929-1bdc-480c-8510-e43a2a862a6e"/>
-    <xsd:import namespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:Access" minOccurs="0"/>
-                <xsd:element ref="ns2:Access_x002f_Info" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e670929-1bdc-480c-8510-e43a2a862a6e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b25c28e6-01a0-48d2-b828-62504f505dd7" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Access" ma:index="18" nillable="true" ma:displayName="Access" ma:description="Who gets access&#10;" ma:format="Dropdown" ma:internalName="Access">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Access_x002f_Info" ma:index="19" nillable="true" ma:displayName="Access/ Info " ma:format="Dropdown" ma:internalName="Access_x002f_Info">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{156fa16d-c7d6-4694-aac4-2bac9e86d8b0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Access xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e1750f8f-64a8-40e8-9e0c-21710cc1a7bb" xsi:nil="true"/>
-    <Access_x002f_Info xmlns="7e670929-1bdc-480c-8510-e43a2a862a6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{945D8665-BB08-45C8-840D-18D1435796C1}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BD9ABE0-6CF6-4F1E-898D-882E0269A924}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B5FEB4-9DED-4683-B971-45C8DEFC8855}"/>
 </file>
--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -4851,7 +4851,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26.25" customHeight="1" s="50">
       <c r="A4" s="89" t="inlineStr">
         <is>
@@ -6203,8 +6202,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="50">
       <c r="A19" s="57" t="inlineStr">
         <is>
@@ -6278,8 +6275,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="50">
       <c r="A24" s="57" t="inlineStr">
         <is>
@@ -6388,7 +6383,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="57" t="inlineStr">
         <is>
@@ -6412,7 +6406,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="26.25" customHeight="1" s="50">
       <c r="A7" s="60" t="inlineStr">
         <is>
@@ -6656,7 +6649,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="57" t="inlineStr">
         <is>
@@ -6715,7 +6707,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="48" customHeight="1" s="50">
       <c r="A4" s="68" t="inlineStr">
         <is>
@@ -6788,7 +6779,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="50">
       <c r="A11" s="57" t="inlineStr">
         <is>
@@ -6831,7 +6821,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="50">
       <c r="A18" s="57" t="inlineStr">
         <is>
@@ -6891,7 +6880,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="60" t="inlineStr">
         <is>
@@ -7095,7 +7083,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="50">
       <c r="A3" s="60" t="inlineStr">
         <is>
@@ -7298,7 +7285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J367"/>
+  <dimension ref="A1:J368"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="49" min="1" max="1"/>
@@ -7320,7 +7307,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="26.25" customHeight="1" s="50">
       <c r="A3" s="60" t="inlineStr">
         <is>
@@ -15756,11 +15742,11 @@
         <v>3</v>
       </c>
       <c r="H306" s="79">
-        <f>F306/G306</f>
+        <f>F322/G322</f>
         <v/>
       </c>
       <c r="I306" s="49">
-        <f>IF(H306&gt;=E306,"Yes","No")</f>
+        <f>IF(H322&gt;=E322,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -15788,11 +15774,11 @@
         <v>1</v>
       </c>
       <c r="H307" s="79">
-        <f>F307/G307</f>
+        <f>F323/G323</f>
         <v/>
       </c>
       <c r="I307" s="49">
-        <f>IF(H307&gt;=E307,"Yes","No")</f>
+        <f>IF(H323&gt;=E323,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -15820,11 +15806,11 @@
         <v>1</v>
       </c>
       <c r="H308" s="79">
-        <f>F308/G308</f>
+        <f>F324/G324</f>
         <v/>
       </c>
       <c r="I308" s="49">
-        <f>IF(H308&gt;=E308,"Yes","No")</f>
+        <f>IF(H324&gt;=E324,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -15852,11 +15838,11 @@
         <v>13</v>
       </c>
       <c r="H309" s="79">
-        <f>F309/G309</f>
+        <f>F325/G325</f>
         <v/>
       </c>
       <c r="I309" s="49">
-        <f>IF(H309&gt;=E309,"Yes","No")</f>
+        <f>IF(H325&gt;=E325,"Yes","No")</f>
         <v/>
       </c>
       <c r="J309" s="49" t="inlineStr">
@@ -15889,11 +15875,11 @@
         <v>1</v>
       </c>
       <c r="H310" s="79">
-        <f>F310/G310</f>
+        <f>F326/G326</f>
         <v/>
       </c>
       <c r="I310" s="49">
-        <f>IF(H310&gt;=E310,"Yes","No")</f>
+        <f>IF(H326&gt;=E326,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -15921,11 +15907,11 @@
         <v>3</v>
       </c>
       <c r="H311" s="79">
-        <f>F311/G311</f>
+        <f>F327/G327</f>
         <v/>
       </c>
       <c r="I311" s="49">
-        <f>IF(H311&gt;=E311,"Yes","No")</f>
+        <f>IF(H327&gt;=E327,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -15953,11 +15939,11 @@
         <v>4</v>
       </c>
       <c r="H312" s="79">
-        <f>F312/G312</f>
+        <f>F328/G328</f>
         <v/>
       </c>
       <c r="I312" s="49">
-        <f>IF(H312&gt;=E312,"Yes","No")</f>
+        <f>IF(H328&gt;=E328,"Yes","No")</f>
         <v/>
       </c>
       <c r="J312" s="49" t="inlineStr">
@@ -15990,11 +15976,11 @@
         <v>2</v>
       </c>
       <c r="H313" s="79">
-        <f>F313/G313</f>
+        <f>F329/G329</f>
         <v/>
       </c>
       <c r="I313" s="49">
-        <f>IF(H313&gt;=E313,"Yes","No")</f>
+        <f>IF(H329&gt;=E329,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16022,11 +16008,11 @@
         <v>1</v>
       </c>
       <c r="H314" s="79">
-        <f>F314/G314</f>
+        <f>F330/G330</f>
         <v/>
       </c>
       <c r="I314" s="49">
-        <f>IF(H314&gt;=E314,"Yes","No")</f>
+        <f>IF(H330&gt;=E330,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16054,11 +16040,11 @@
         <v>2</v>
       </c>
       <c r="H315" s="79">
-        <f>F315/G315</f>
+        <f>F331/G331</f>
         <v/>
       </c>
       <c r="I315" s="49">
-        <f>IF(H315&gt;=E315,"Yes","No")</f>
+        <f>IF(H331&gt;=E331,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16086,11 +16072,11 @@
         <v>6</v>
       </c>
       <c r="H316" s="79">
-        <f>F316/G316</f>
+        <f>F332/G332</f>
         <v/>
       </c>
       <c r="I316" s="49">
-        <f>IF(H316&gt;=E316,"Yes","No")</f>
+        <f>IF(H332&gt;=E332,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16100,7 +16086,7 @@
       </c>
       <c r="B317" s="49" t="inlineStr">
         <is>
-          <t>Coromandel Mountains Company Limited</t>
+          <t>Baking Tech</t>
         </is>
       </c>
       <c r="C317" s="49" t="inlineStr">
@@ -16112,17 +16098,17 @@
         <v>0.95</v>
       </c>
       <c r="F317" s="49" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="G317" s="49" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H317" s="79">
-        <f>F317/G317</f>
+        <f>F333/G333</f>
         <v/>
       </c>
       <c r="I317" s="49">
-        <f>IF(H317&gt;=E317,"Yes","No")</f>
+        <f>IF(H333&gt;=E333,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16132,7 +16118,7 @@
       </c>
       <c r="B318" s="49" t="inlineStr">
         <is>
-          <t>EcoPallets</t>
+          <t>Coromandel Mountains Company Limited</t>
         </is>
       </c>
       <c r="C318" s="49" t="inlineStr">
@@ -16144,23 +16130,18 @@
         <v>0.95</v>
       </c>
       <c r="F318" s="49" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="G318" s="49" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H318" s="79">
-        <f>F318/G318</f>
+        <f>F334/G334</f>
         <v/>
       </c>
       <c r="I318" s="49">
-        <f>IF(H318&gt;=E318,"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="J318" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
+        <f>IF(H334&gt;=E334,"Yes","No")</f>
+        <v/>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" s="50">
@@ -16169,7 +16150,7 @@
       </c>
       <c r="B319" s="49" t="inlineStr">
         <is>
-          <t>Flo &amp; Frankie</t>
+          <t>EcoPallets</t>
         </is>
       </c>
       <c r="C319" s="49" t="inlineStr">
@@ -16184,14 +16165,14 @@
         <v>11</v>
       </c>
       <c r="G319" s="49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H319" s="79">
-        <f>F319/G319</f>
+        <f>F335/G335</f>
         <v/>
       </c>
       <c r="I319" s="49">
-        <f>IF(H319&gt;=E319,"Yes","No")</f>
+        <f>IF(H335&gt;=E335,"Yes","No")</f>
         <v/>
       </c>
       <c r="J319" s="49" t="inlineStr">
@@ -16206,7 +16187,7 @@
       </c>
       <c r="B320" s="49" t="inlineStr">
         <is>
-          <t>Gym Equip</t>
+          <t>Flo &amp; Frankie</t>
         </is>
       </c>
       <c r="C320" s="49" t="inlineStr">
@@ -16218,23 +16199,18 @@
         <v>0.95</v>
       </c>
       <c r="F320" s="49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G320" s="49" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H320" s="79">
-        <f>F320/G320</f>
+        <f>F336/G336</f>
         <v/>
       </c>
       <c r="I320" s="49">
-        <f>IF(H320&gt;=E320,"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="J320" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
+        <f>IF(H336&gt;=E336,"Yes","No")</f>
+        <v/>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1" s="50">
@@ -16243,7 +16219,7 @@
       </c>
       <c r="B321" s="49" t="inlineStr">
         <is>
-          <t>Jock Freight - SECA</t>
+          <t>Gym Equip</t>
         </is>
       </c>
       <c r="C321" s="49" t="inlineStr">
@@ -16255,18 +16231,23 @@
         <v>0.95</v>
       </c>
       <c r="F321" s="49" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G321" s="49" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H321" s="79">
-        <f>F321/G321</f>
+        <f>F337/G337</f>
         <v/>
       </c>
       <c r="I321" s="49">
-        <f>IF(H321&gt;=E321,"Yes","No")</f>
-        <v/>
+        <f>IF(H337&gt;=E337,"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="J321" s="49" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="322" ht="15" customHeight="1" s="50">
@@ -16275,7 +16256,7 @@
       </c>
       <c r="B322" s="49" t="inlineStr">
         <is>
-          <t>Logwin - Sikla</t>
+          <t>Jock Freight - SECA</t>
         </is>
       </c>
       <c r="C322" s="49" t="inlineStr">
@@ -16287,18 +16268,23 @@
         <v>0.95</v>
       </c>
       <c r="F322" s="49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G322" s="49" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H322" s="79">
-        <f>F322/G322</f>
+        <f>F338/G338</f>
         <v/>
       </c>
       <c r="I322" s="49">
-        <f>IF(H322&gt;=E322,"Yes","No")</f>
-        <v/>
+        <f>IF(H338&gt;=E338,"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="J322" s="49" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="323" ht="15" customHeight="1" s="50">
@@ -16307,7 +16293,7 @@
       </c>
       <c r="B323" s="49" t="inlineStr">
         <is>
-          <t>Made Group NZ</t>
+          <t>Logwin - Sikla</t>
         </is>
       </c>
       <c r="C323" s="49" t="inlineStr">
@@ -16319,17 +16305,17 @@
         <v>0.95</v>
       </c>
       <c r="F323" s="49" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G323" s="49" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H323" s="79">
-        <f>F323/G323</f>
+        <f>F339/G339</f>
         <v/>
       </c>
       <c r="I323" s="49">
-        <f>IF(H323&gt;=E323,"Yes","No")</f>
+        <f>IF(H339&gt;=E339,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16339,7 +16325,7 @@
       </c>
       <c r="B324" s="49" t="inlineStr">
         <is>
-          <t>May Eleven NZ</t>
+          <t>Made Group NZ</t>
         </is>
       </c>
       <c r="C324" s="49" t="inlineStr">
@@ -16351,17 +16337,17 @@
         <v>0.95</v>
       </c>
       <c r="F324" s="49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G324" s="49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H324" s="79">
-        <f>F324/G324</f>
+        <f>F340/G340</f>
         <v/>
       </c>
       <c r="I324" s="49">
-        <f>IF(H324&gt;=E324,"Yes","No")</f>
+        <f>IF(H340&gt;=E340,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16371,7 +16357,7 @@
       </c>
       <c r="B325" s="49" t="inlineStr">
         <is>
-          <t>Oceanbridge</t>
+          <t>May Eleven NZ</t>
         </is>
       </c>
       <c r="C325" s="49" t="inlineStr">
@@ -16383,17 +16369,17 @@
         <v>0.95</v>
       </c>
       <c r="F325" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G325" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H325" s="79">
-        <f>F325/G325</f>
+        <f>F341/G341</f>
         <v/>
       </c>
       <c r="I325" s="49">
-        <f>IF(H325&gt;=E325,"Yes","No")</f>
+        <f>IF(H341&gt;=E341,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16403,7 +16389,7 @@
       </c>
       <c r="B326" s="49" t="inlineStr">
         <is>
-          <t>Oricom</t>
+          <t>Oceanbridge</t>
         </is>
       </c>
       <c r="C326" s="49" t="inlineStr">
@@ -16415,17 +16401,17 @@
         <v>0.95</v>
       </c>
       <c r="F326" s="49" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="G326" s="49" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="H326" s="79">
-        <f>F326/G326</f>
+        <f>F342/G342</f>
         <v/>
       </c>
       <c r="I326" s="49">
-        <f>IF(H326&gt;=E326,"Yes","No")</f>
+        <f>IF(H342&gt;=E342,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16435,7 +16421,7 @@
       </c>
       <c r="B327" s="49" t="inlineStr">
         <is>
-          <t>Purify Me</t>
+          <t>Oricom</t>
         </is>
       </c>
       <c r="C327" s="49" t="inlineStr">
@@ -16447,17 +16433,17 @@
         <v>0.95</v>
       </c>
       <c r="F327" s="49" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G327" s="49" t="n">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="H327" s="79">
-        <f>F327/G327</f>
+        <f>F343/G343</f>
         <v/>
       </c>
       <c r="I327" s="49">
-        <f>IF(H327&gt;=E327,"Yes","No")</f>
+        <f>IF(H343&gt;=E343,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16467,7 +16453,7 @@
       </c>
       <c r="B328" s="49" t="inlineStr">
         <is>
-          <t>Salt Shark</t>
+          <t>Purify Me</t>
         </is>
       </c>
       <c r="C328" s="49" t="inlineStr">
@@ -16479,23 +16465,18 @@
         <v>0.95</v>
       </c>
       <c r="F328" s="49" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G328" s="49" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="H328" s="79">
-        <f>F328/G328</f>
+        <f>F344/G344</f>
         <v/>
       </c>
       <c r="I328" s="49">
-        <f>IF(H328&gt;=E328,"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="J328" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
+        <f>IF(H344&gt;=E344,"Yes","No")</f>
+        <v/>
       </c>
     </row>
     <row r="329" ht="15" customHeight="1" s="50">
@@ -16504,7 +16485,7 @@
       </c>
       <c r="B329" s="49" t="inlineStr">
         <is>
-          <t>Samsung Batteries CP</t>
+          <t>Salt Shark</t>
         </is>
       </c>
       <c r="C329" s="49" t="inlineStr">
@@ -16516,23 +16497,18 @@
         <v>0.95</v>
       </c>
       <c r="F329" s="49" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="G329" s="49" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="H329" s="79">
-        <f>F329/G329</f>
+        <f>F345/G345</f>
         <v/>
       </c>
       <c r="I329" s="49">
-        <f>IF(H329&gt;=E329,"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="J329" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
+        <f>IF(H345&gt;=E345,"Yes","No")</f>
+        <v/>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1" s="50">
@@ -16541,7 +16517,7 @@
       </c>
       <c r="B330" s="49" t="inlineStr">
         <is>
-          <t>Simply Clean</t>
+          <t>Samsung Batteries CP</t>
         </is>
       </c>
       <c r="C330" s="49" t="inlineStr">
@@ -16553,17 +16529,17 @@
         <v>0.95</v>
       </c>
       <c r="F330" s="49" t="n">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="G330" s="49" t="n">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="H330" s="79">
-        <f>F330/G330</f>
+        <f>F346/G346</f>
         <v/>
       </c>
       <c r="I330" s="49">
-        <f>IF(H330&gt;=E330,"Yes","No")</f>
+        <f>IF(H346&gt;=E346,"Yes","No")</f>
         <v/>
       </c>
       <c r="J330" s="49" t="inlineStr">
@@ -16578,7 +16554,7 @@
       </c>
       <c r="B331" s="49" t="inlineStr">
         <is>
-          <t>Stryx</t>
+          <t>Simply Clean</t>
         </is>
       </c>
       <c r="C331" s="49" t="inlineStr">
@@ -16590,17 +16566,17 @@
         <v>0.95</v>
       </c>
       <c r="F331" s="49" t="n">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="G331" s="49" t="n">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="H331" s="79">
-        <f>F331/G331</f>
+        <f>F347/G347</f>
         <v/>
       </c>
       <c r="I331" s="49">
-        <f>IF(H331&gt;=E331,"Yes","No")</f>
+        <f>IF(H347&gt;=E347,"Yes","No")</f>
         <v/>
       </c>
       <c r="J331" s="49" t="inlineStr">
@@ -16615,7 +16591,7 @@
       </c>
       <c r="B332" s="49" t="inlineStr">
         <is>
-          <t>Vixxen</t>
+          <t>Stryx</t>
         </is>
       </c>
       <c r="C332" s="49" t="inlineStr">
@@ -16627,18 +16603,23 @@
         <v>0.95</v>
       </c>
       <c r="F332" s="49" t="n">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="G332" s="49" t="n">
-        <v>365</v>
+        <v>37</v>
       </c>
       <c r="H332" s="79">
-        <f>F332/G332</f>
+        <f>F348/G348</f>
         <v/>
       </c>
       <c r="I332" s="49">
-        <f>IF(H332&gt;=E332,"Yes","No")</f>
-        <v/>
+        <f>IF(H348&gt;=E348,"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="J332" s="49" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1" s="50">
@@ -16647,29 +16628,29 @@
       </c>
       <c r="B333" s="49" t="inlineStr">
         <is>
-          <t>Aleger Studio</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="C333" s="49" t="inlineStr">
         <is>
-          <t>Order Accuracy by Unit</t>
+          <t>Order Cut Off</t>
         </is>
       </c>
       <c r="E333" s="79" t="n">
-        <v>0.995</v>
+        <v>0.95</v>
       </c>
       <c r="F333" s="49" t="n">
-        <v>8</v>
+        <v>424</v>
       </c>
       <c r="G333" s="49" t="n">
-        <v>8</v>
+        <v>426</v>
       </c>
       <c r="H333" s="79">
-        <f>F333/G333</f>
+        <f>F349/G349</f>
         <v/>
       </c>
       <c r="I333" s="49">
-        <f>IF(H333&gt;=E333,"Yes","No")</f>
+        <f>IF(H349&gt;=E349,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16679,7 +16660,7 @@
       </c>
       <c r="B334" s="49" t="inlineStr">
         <is>
-          <t>Baking Tech</t>
+          <t>Aleger Studio</t>
         </is>
       </c>
       <c r="C334" s="49" t="inlineStr">
@@ -16691,17 +16672,17 @@
         <v>0.995</v>
       </c>
       <c r="F334" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G334" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H334" s="79">
-        <f>F334/G334</f>
+        <f>F350/G350</f>
         <v/>
       </c>
       <c r="I334" s="49">
-        <f>IF(H334&gt;=E334,"Yes","No")</f>
+        <f>IF(H350&gt;=E350,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16711,7 +16692,7 @@
       </c>
       <c r="B335" s="49" t="inlineStr">
         <is>
-          <t>Coromandel Mountains Company Limited</t>
+          <t>Baking Tech</t>
         </is>
       </c>
       <c r="C335" s="49" t="inlineStr">
@@ -16723,17 +16704,17 @@
         <v>0.995</v>
       </c>
       <c r="F335" s="49" t="n">
-        <v>715</v>
+        <v>1</v>
       </c>
       <c r="G335" s="49" t="n">
-        <v>715</v>
+        <v>1</v>
       </c>
       <c r="H335" s="79">
-        <f>F335/G335</f>
+        <f>F351/G351</f>
         <v/>
       </c>
       <c r="I335" s="49">
-        <f>IF(H335&gt;=E335,"Yes","No")</f>
+        <f>IF(H351&gt;=E351,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16743,7 +16724,7 @@
       </c>
       <c r="B336" s="49" t="inlineStr">
         <is>
-          <t>EcoPallets</t>
+          <t>Coromandel Mountains Company Limited</t>
         </is>
       </c>
       <c r="C336" s="49" t="inlineStr">
@@ -16755,17 +16736,17 @@
         <v>0.995</v>
       </c>
       <c r="F336" s="49" t="n">
-        <v>484</v>
+        <v>715</v>
       </c>
       <c r="G336" s="49" t="n">
-        <v>484</v>
+        <v>715</v>
       </c>
       <c r="H336" s="79">
-        <f>F336/G336</f>
+        <f>F352/G352</f>
         <v/>
       </c>
       <c r="I336" s="49">
-        <f>IF(H336&gt;=E336,"Yes","No")</f>
+        <f>IF(H352&gt;=E352,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16775,7 +16756,7 @@
       </c>
       <c r="B337" s="49" t="inlineStr">
         <is>
-          <t>Flo &amp; Frankie</t>
+          <t>EcoPallets</t>
         </is>
       </c>
       <c r="C337" s="49" t="inlineStr">
@@ -16787,17 +16768,17 @@
         <v>0.995</v>
       </c>
       <c r="F337" s="49" t="n">
-        <v>633</v>
+        <v>484</v>
       </c>
       <c r="G337" s="49" t="n">
-        <v>633</v>
+        <v>484</v>
       </c>
       <c r="H337" s="79">
-        <f>F337/G337</f>
+        <f>F353/G353</f>
         <v/>
       </c>
       <c r="I337" s="49">
-        <f>IF(H337&gt;=E337,"Yes","No")</f>
+        <f>IF(H353&gt;=E353,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16807,7 +16788,7 @@
       </c>
       <c r="B338" s="49" t="inlineStr">
         <is>
-          <t>Gym Equip</t>
+          <t>Flo &amp; Frankie</t>
         </is>
       </c>
       <c r="C338" s="49" t="inlineStr">
@@ -16819,17 +16800,17 @@
         <v>0.995</v>
       </c>
       <c r="F338" s="49" t="n">
-        <v>384</v>
+        <v>633</v>
       </c>
       <c r="G338" s="49" t="n">
-        <v>384</v>
+        <v>633</v>
       </c>
       <c r="H338" s="79">
-        <f>F338/G338</f>
+        <f>F354/G354</f>
         <v/>
       </c>
       <c r="I338" s="49">
-        <f>IF(H338&gt;=E338,"Yes","No")</f>
+        <f>IF(H354&gt;=E354,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16839,7 +16820,7 @@
       </c>
       <c r="B339" s="49" t="inlineStr">
         <is>
-          <t>Interior Images</t>
+          <t>Gym Equip</t>
         </is>
       </c>
       <c r="C339" s="49" t="inlineStr">
@@ -16851,17 +16832,17 @@
         <v>0.995</v>
       </c>
       <c r="F339" s="49" t="n">
-        <v>14</v>
+        <v>384</v>
       </c>
       <c r="G339" s="49" t="n">
-        <v>14</v>
+        <v>384</v>
       </c>
       <c r="H339" s="79">
-        <f>F339/G339</f>
+        <f>F355/G355</f>
         <v/>
       </c>
       <c r="I339" s="49">
-        <f>IF(H339&gt;=E339,"Yes","No")</f>
+        <f>IF(H355&gt;=E355,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16871,7 +16852,7 @@
       </c>
       <c r="B340" s="49" t="inlineStr">
         <is>
-          <t>Jock Freight - SECA</t>
+          <t>Interior Images</t>
         </is>
       </c>
       <c r="C340" s="49" t="inlineStr">
@@ -16883,17 +16864,17 @@
         <v>0.995</v>
       </c>
       <c r="F340" s="49" t="n">
-        <v>972</v>
+        <v>14</v>
       </c>
       <c r="G340" s="49" t="n">
-        <v>972</v>
+        <v>14</v>
       </c>
       <c r="H340" s="79">
-        <f>F340/G340</f>
+        <f>F356/G356</f>
         <v/>
       </c>
       <c r="I340" s="49">
-        <f>IF(H340&gt;=E340,"Yes","No")</f>
+        <f>IF(H356&gt;=E356,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16903,7 +16884,7 @@
       </c>
       <c r="B341" s="49" t="inlineStr">
         <is>
-          <t>Logwin - Sikla</t>
+          <t>Jock Freight - SECA</t>
         </is>
       </c>
       <c r="C341" s="49" t="inlineStr">
@@ -16915,17 +16896,17 @@
         <v>0.995</v>
       </c>
       <c r="F341" s="49" t="n">
-        <v>5163</v>
+        <v>972</v>
       </c>
       <c r="G341" s="49" t="n">
-        <v>5163</v>
+        <v>972</v>
       </c>
       <c r="H341" s="79">
-        <f>F341/G341</f>
+        <f>F357/G357</f>
         <v/>
       </c>
       <c r="I341" s="49">
-        <f>IF(H341&gt;=E341,"Yes","No")</f>
+        <f>IF(H357&gt;=E357,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16935,7 +16916,7 @@
       </c>
       <c r="B342" s="49" t="inlineStr">
         <is>
-          <t>Made Group NZ</t>
+          <t>Logwin - Sikla</t>
         </is>
       </c>
       <c r="C342" s="49" t="inlineStr">
@@ -16947,17 +16928,17 @@
         <v>0.995</v>
       </c>
       <c r="F342" s="49" t="n">
-        <v>14190</v>
+        <v>5163</v>
       </c>
       <c r="G342" s="49" t="n">
-        <v>14190</v>
+        <v>5163</v>
       </c>
       <c r="H342" s="79">
-        <f>F342/G342</f>
+        <f>F358/G358</f>
         <v/>
       </c>
       <c r="I342" s="49">
-        <f>IF(H342&gt;=E342,"Yes","No")</f>
+        <f>IF(H358&gt;=E358,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16967,7 +16948,7 @@
       </c>
       <c r="B343" s="49" t="inlineStr">
         <is>
-          <t>May Eleven NZ</t>
+          <t>Made Group NZ</t>
         </is>
       </c>
       <c r="C343" s="49" t="inlineStr">
@@ -16979,17 +16960,17 @@
         <v>0.995</v>
       </c>
       <c r="F343" s="49" t="n">
-        <v>1500</v>
+        <v>14190</v>
       </c>
       <c r="G343" s="49" t="n">
-        <v>1500</v>
+        <v>14190</v>
       </c>
       <c r="H343" s="79">
-        <f>F343/G343</f>
+        <f>F359/G359</f>
         <v/>
       </c>
       <c r="I343" s="49">
-        <f>IF(H343&gt;=E343,"Yes","No")</f>
+        <f>IF(H359&gt;=E359,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -16999,7 +16980,7 @@
       </c>
       <c r="B344" s="49" t="inlineStr">
         <is>
-          <t>Oceanbridge</t>
+          <t>May Eleven NZ</t>
         </is>
       </c>
       <c r="C344" s="49" t="inlineStr">
@@ -17011,17 +16992,17 @@
         <v>0.995</v>
       </c>
       <c r="F344" s="49" t="n">
-        <v>55</v>
+        <v>1500</v>
       </c>
       <c r="G344" s="49" t="n">
-        <v>55</v>
+        <v>1500</v>
       </c>
       <c r="H344" s="79">
-        <f>F344/G344</f>
+        <f>F360/G360</f>
         <v/>
       </c>
       <c r="I344" s="49">
-        <f>IF(H344&gt;=E344,"Yes","No")</f>
+        <f>IF(H360&gt;=E360,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17031,7 +17012,7 @@
       </c>
       <c r="B345" s="49" t="inlineStr">
         <is>
-          <t>Oricom</t>
+          <t>Oceanbridge</t>
         </is>
       </c>
       <c r="C345" s="49" t="inlineStr">
@@ -17043,17 +17024,17 @@
         <v>0.995</v>
       </c>
       <c r="F345" s="49" t="n">
-        <v>1075</v>
+        <v>55</v>
       </c>
       <c r="G345" s="49" t="n">
-        <v>1075</v>
+        <v>55</v>
       </c>
       <c r="H345" s="79">
-        <f>F345/G345</f>
+        <f>F361/G361</f>
         <v/>
       </c>
       <c r="I345" s="49">
-        <f>IF(H345&gt;=E345,"Yes","No")</f>
+        <f>IF(H361&gt;=E361,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17063,7 +17044,7 @@
       </c>
       <c r="B346" s="49" t="inlineStr">
         <is>
-          <t>Purify Me</t>
+          <t>Oricom</t>
         </is>
       </c>
       <c r="C346" s="49" t="inlineStr">
@@ -17075,17 +17056,17 @@
         <v>0.995</v>
       </c>
       <c r="F346" s="49" t="n">
-        <v>211</v>
+        <v>1075</v>
       </c>
       <c r="G346" s="49" t="n">
-        <v>211</v>
+        <v>1075</v>
       </c>
       <c r="H346" s="79">
-        <f>F346/G346</f>
+        <f>F362/G362</f>
         <v/>
       </c>
       <c r="I346" s="49">
-        <f>IF(H346&gt;=E346,"Yes","No")</f>
+        <f>IF(H362&gt;=E362,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17095,7 +17076,7 @@
       </c>
       <c r="B347" s="49" t="inlineStr">
         <is>
-          <t>Salt Shark</t>
+          <t>Purify Me</t>
         </is>
       </c>
       <c r="C347" s="49" t="inlineStr">
@@ -17107,17 +17088,17 @@
         <v>0.995</v>
       </c>
       <c r="F347" s="49" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="G347" s="49" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H347" s="79">
-        <f>F347/G347</f>
+        <f>F363/G363</f>
         <v/>
       </c>
       <c r="I347" s="49">
-        <f>IF(H347&gt;=E347,"Yes","No")</f>
+        <f>IF(H363&gt;=E363,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17127,7 +17108,7 @@
       </c>
       <c r="B348" s="49" t="inlineStr">
         <is>
-          <t>Samsung Batteries CP</t>
+          <t>Salt Shark</t>
         </is>
       </c>
       <c r="C348" s="49" t="inlineStr">
@@ -17139,17 +17120,17 @@
         <v>0.995</v>
       </c>
       <c r="F348" s="49" t="n">
-        <v>1329</v>
+        <v>336</v>
       </c>
       <c r="G348" s="49" t="n">
-        <v>1329</v>
+        <v>336</v>
       </c>
       <c r="H348" s="79">
-        <f>F348/G348</f>
+        <f>F364/G364</f>
         <v/>
       </c>
       <c r="I348" s="49">
-        <f>IF(H348&gt;=E348,"Yes","No")</f>
+        <f>IF(H364&gt;=E364,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17159,7 +17140,7 @@
       </c>
       <c r="B349" s="49" t="inlineStr">
         <is>
-          <t>Simply Clean</t>
+          <t>Samsung Batteries CP</t>
         </is>
       </c>
       <c r="C349" s="49" t="inlineStr">
@@ -17171,17 +17152,17 @@
         <v>0.995</v>
       </c>
       <c r="F349" s="49" t="n">
-        <v>9658</v>
+        <v>1329</v>
       </c>
       <c r="G349" s="49" t="n">
-        <v>9658</v>
+        <v>1329</v>
       </c>
       <c r="H349" s="79">
-        <f>F349/G349</f>
+        <f>F365/G365</f>
         <v/>
       </c>
       <c r="I349" s="49">
-        <f>IF(H349&gt;=E349,"Yes","No")</f>
+        <f>IF(H365&gt;=E365,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17191,7 +17172,7 @@
       </c>
       <c r="B350" s="49" t="inlineStr">
         <is>
-          <t>Stryx</t>
+          <t>Simply Clean</t>
         </is>
       </c>
       <c r="C350" s="49" t="inlineStr">
@@ -17203,17 +17184,17 @@
         <v>0.995</v>
       </c>
       <c r="F350" s="49" t="n">
-        <v>56</v>
+        <v>9658</v>
       </c>
       <c r="G350" s="49" t="n">
-        <v>56</v>
+        <v>9658</v>
       </c>
       <c r="H350" s="79">
-        <f>F350/G350</f>
+        <f>F366/G366</f>
         <v/>
       </c>
       <c r="I350" s="49">
-        <f>IF(H350&gt;=E350,"Yes","No")</f>
+        <f>IF(H366&gt;=E366,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17223,7 +17204,7 @@
       </c>
       <c r="B351" s="49" t="inlineStr">
         <is>
-          <t>Vixxen</t>
+          <t>Stryx</t>
         </is>
       </c>
       <c r="C351" s="49" t="inlineStr">
@@ -17235,49 +17216,49 @@
         <v>0.995</v>
       </c>
       <c r="F351" s="49" t="n">
-        <v>9761</v>
+        <v>56</v>
       </c>
       <c r="G351" s="49" t="n">
-        <v>9766</v>
+        <v>56</v>
       </c>
       <c r="H351" s="79">
-        <f>F351/G351</f>
+        <f>F367/G367</f>
         <v/>
       </c>
       <c r="I351" s="49">
-        <f>IF(H351&gt;=E351,"Yes","No")</f>
+        <f>IF(H367&gt;=E367,"Yes","No")</f>
         <v/>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="90" t="n">
+      <c r="A352" s="78" t="n">
         <v>46266</v>
       </c>
       <c r="B352" s="49" t="inlineStr">
         <is>
-          <t>Aleger Studio</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="C352" s="49" t="inlineStr">
         <is>
-          <t>Freight DIFOT</t>
-        </is>
-      </c>
-      <c r="E352" s="49" t="n">
-        <v>0.95</v>
+          <t>Order Accuracy by Unit</t>
+        </is>
+      </c>
+      <c r="E352" s="79" t="n">
+        <v>0.995</v>
       </c>
       <c r="F352" s="49" t="n">
-        <v>6</v>
+        <v>10722</v>
       </c>
       <c r="G352" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="H352" s="49">
-        <f>F352/G352</f>
+        <v>10741</v>
+      </c>
+      <c r="H352" s="79">
+        <f>F368/G368</f>
         <v/>
       </c>
       <c r="I352" s="49">
-        <f>IF(H352&gt;=E352,"Yes","No")</f>
+        <f>IF(H368&gt;=E368,"Yes","No")</f>
         <v/>
       </c>
     </row>
@@ -17285,71 +17266,66 @@
       <c r="A353" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B353" s="49" t="inlineStr">
-        <is>
-          <t>Coromandel Mountains Company Limited</t>
-        </is>
-      </c>
-      <c r="C353" s="49" t="inlineStr">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Aleger Studio</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E353" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F353" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="G353" s="49" t="n">
-        <v>34</v>
-      </c>
-      <c r="H353" s="49">
+      <c r="E353" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F353" t="n">
+        <v>6</v>
+      </c>
+      <c r="G353" t="n">
+        <v>6</v>
+      </c>
+      <c r="H353">
         <f>F353/G353</f>
         <v/>
       </c>
-      <c r="I353" s="49">
+      <c r="I353">
         <f>IF(H353&gt;=E353,"Yes","No")</f>
         <v/>
-      </c>
-      <c r="J353" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B354" s="49" t="inlineStr">
-        <is>
-          <t>EcoPallets</t>
-        </is>
-      </c>
-      <c r="C354" s="49" t="inlineStr">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E354" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F354" s="49" t="n">
-        <v>7</v>
-      </c>
-      <c r="G354" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="H354" s="49">
+      <c r="E354" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F354" t="n">
+        <v>36</v>
+      </c>
+      <c r="G354" t="n">
+        <v>38</v>
+      </c>
+      <c r="H354">
         <f>F354/G354</f>
         <v/>
       </c>
-      <c r="I354" s="49">
+      <c r="I354">
         <f>IF(H354&gt;=E354,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J354" s="49" t="inlineStr">
+      <c r="J354" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17359,34 +17335,34 @@
       <c r="A355" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B355" s="49" t="inlineStr">
-        <is>
-          <t>Flo &amp; Frankie</t>
-        </is>
-      </c>
-      <c r="C355" s="49" t="inlineStr">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>EcoPallets</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E355" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F355" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="G355" s="49" t="n">
-        <v>13</v>
-      </c>
-      <c r="H355" s="49">
+      <c r="E355" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F355" t="n">
+        <v>6</v>
+      </c>
+      <c r="G355" t="n">
+        <v>7</v>
+      </c>
+      <c r="H355">
         <f>F355/G355</f>
         <v/>
       </c>
-      <c r="I355" s="49">
+      <c r="I355">
         <f>IF(H355&gt;=E355,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J355" s="49" t="inlineStr">
+      <c r="J355" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17396,34 +17372,34 @@
       <c r="A356" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B356" s="49" t="inlineStr">
-        <is>
-          <t>Gym Equip</t>
-        </is>
-      </c>
-      <c r="C356" s="49" t="inlineStr">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Flo &amp; Frankie</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E356" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F356" s="49" t="n">
-        <v>17</v>
-      </c>
-      <c r="G356" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="H356" s="49">
+      <c r="E356" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F356" t="n">
+        <v>11</v>
+      </c>
+      <c r="G356" t="n">
+        <v>13</v>
+      </c>
+      <c r="H356">
         <f>F356/G356</f>
         <v/>
       </c>
-      <c r="I356" s="49">
+      <c r="I356">
         <f>IF(H356&gt;=E356,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J356" s="49" t="inlineStr">
+      <c r="J356" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17433,131 +17409,136 @@
       <c r="A357" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B357" s="49" t="inlineStr">
-        <is>
-          <t>Interior Images</t>
-        </is>
-      </c>
-      <c r="C357" s="49" t="inlineStr">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Gym Equip</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E357" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F357" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G357" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H357" s="49">
+      <c r="E357" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F357" t="n">
+        <v>17</v>
+      </c>
+      <c r="G357" t="n">
+        <v>19</v>
+      </c>
+      <c r="H357">
         <f>F357/G357</f>
         <v/>
       </c>
-      <c r="I357" s="49">
+      <c r="I357">
         <f>IF(H357&gt;=E357,"Yes","No")</f>
         <v/>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B358" s="49" t="inlineStr">
-        <is>
-          <t>Jock Freight - SECA</t>
-        </is>
-      </c>
-      <c r="C358" s="49" t="inlineStr">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Interior Images</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E358" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F358" s="49" t="n">
-        <v>9</v>
-      </c>
-      <c r="G358" s="49" t="n">
-        <v>11</v>
-      </c>
-      <c r="H358" s="49">
+      <c r="E358" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1</v>
+      </c>
+      <c r="G358" t="n">
+        <v>1</v>
+      </c>
+      <c r="H358">
         <f>F358/G358</f>
         <v/>
       </c>
-      <c r="I358" s="49">
+      <c r="I358">
         <f>IF(H358&gt;=E358,"Yes","No")</f>
         <v/>
-      </c>
-      <c r="J358" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B359" s="49" t="inlineStr">
-        <is>
-          <t>Logwin - Sikla</t>
-        </is>
-      </c>
-      <c r="C359" s="49" t="inlineStr">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Jock Freight - SECA</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E359" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F359" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="G359" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="H359" s="49">
+      <c r="E359" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F359" t="n">
+        <v>8</v>
+      </c>
+      <c r="G359" t="n">
+        <v>9</v>
+      </c>
+      <c r="H359">
         <f>F359/G359</f>
         <v/>
       </c>
-      <c r="I359" s="49">
+      <c r="I359">
         <f>IF(H359&gt;=E359,"Yes","No")</f>
         <v/>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B360" s="49" t="inlineStr">
-        <is>
-          <t>Made Group NZ</t>
-        </is>
-      </c>
-      <c r="C360" s="49" t="inlineStr">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Logwin - Sikla</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E360" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F360" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G360" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="H360" s="49">
+      <c r="E360" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F360" t="n">
+        <v>6</v>
+      </c>
+      <c r="G360" t="n">
+        <v>6</v>
+      </c>
+      <c r="H360">
         <f>F360/G360</f>
         <v/>
       </c>
-      <c r="I360" s="49">
+      <c r="I360">
         <f>IF(H360&gt;=E360,"Yes","No")</f>
         <v/>
       </c>
@@ -17566,30 +17547,30 @@
       <c r="A361" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B361" s="49" t="inlineStr">
-        <is>
-          <t>May Eleven NZ</t>
-        </is>
-      </c>
-      <c r="C361" s="49" t="inlineStr">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Made Group NZ</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E361" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F361" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="G361" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="H361" s="49">
+      <c r="E361" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F361" t="n">
+        <v>4</v>
+      </c>
+      <c r="G361" t="n">
+        <v>4</v>
+      </c>
+      <c r="H361">
         <f>F361/G361</f>
         <v/>
       </c>
-      <c r="I361" s="49">
+      <c r="I361">
         <f>IF(H361&gt;=E361,"Yes","No")</f>
         <v/>
       </c>
@@ -17598,204 +17579,246 @@
       <c r="A362" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B362" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="C362" s="49" t="inlineStr">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>May Eleven NZ</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E362" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F362" s="49" t="n">
-        <v>75</v>
-      </c>
-      <c r="G362" s="49" t="n">
-        <v>79</v>
-      </c>
-      <c r="H362" s="49">
+      <c r="E362" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F362" t="n">
+        <v>2</v>
+      </c>
+      <c r="G362" t="n">
+        <v>2</v>
+      </c>
+      <c r="H362">
         <f>F362/G362</f>
         <v/>
       </c>
-      <c r="I362" s="49">
+      <c r="I362">
         <f>IF(H362&gt;=E362,"Yes","No")</f>
         <v/>
-      </c>
-      <c r="J362" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B363" s="49" t="inlineStr">
-        <is>
-          <t>Purify Me</t>
-        </is>
-      </c>
-      <c r="C363" s="49" t="inlineStr">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E363" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F363" s="49" t="n">
-        <v>46</v>
-      </c>
-      <c r="G363" s="49" t="n">
-        <v>48</v>
-      </c>
-      <c r="H363" s="49">
+      <c r="E363" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F363" t="n">
+        <v>84</v>
+      </c>
+      <c r="G363" t="n">
+        <v>91</v>
+      </c>
+      <c r="H363">
         <f>F363/G363</f>
         <v/>
       </c>
-      <c r="I363" s="49">
+      <c r="I363">
         <f>IF(H363&gt;=E363,"Yes","No")</f>
         <v/>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B364" s="49" t="inlineStr">
-        <is>
-          <t>Salt Shark</t>
-        </is>
-      </c>
-      <c r="C364" s="49" t="inlineStr">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Purify Me</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E364" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F364" s="49" t="n">
-        <v>38</v>
-      </c>
-      <c r="G364" s="49" t="n">
-        <v>39</v>
-      </c>
-      <c r="H364" s="49">
+      <c r="E364" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F364" t="n">
+        <v>48</v>
+      </c>
+      <c r="G364" t="n">
+        <v>53</v>
+      </c>
+      <c r="H364">
         <f>F364/G364</f>
         <v/>
       </c>
-      <c r="I364" s="49">
+      <c r="I364">
         <f>IF(H364&gt;=E364,"Yes","No")</f>
         <v/>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B365" s="49" t="inlineStr">
-        <is>
-          <t>Simply Clean</t>
-        </is>
-      </c>
-      <c r="C365" s="49" t="inlineStr">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E365" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F365" s="49" t="n">
-        <v>81</v>
-      </c>
-      <c r="G365" s="49" t="n">
-        <v>88</v>
-      </c>
-      <c r="H365" s="49">
+      <c r="E365" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F365" t="n">
+        <v>41</v>
+      </c>
+      <c r="G365" t="n">
+        <v>43</v>
+      </c>
+      <c r="H365">
         <f>F365/G365</f>
         <v/>
       </c>
-      <c r="I365" s="49">
+      <c r="I365">
         <f>IF(H365&gt;=E365,"Yes","No")</f>
         <v/>
-      </c>
-      <c r="J365" s="49" t="inlineStr">
-        <is>
-          <t>Below target - investigate root cause and add to next month's action plan</t>
-        </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B366" s="49" t="inlineStr">
-        <is>
-          <t>Stryx</t>
-        </is>
-      </c>
-      <c r="C366" s="49" t="inlineStr">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Simply Clean</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E366" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F366" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="G366" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="H366" s="49">
+      <c r="E366" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F366" t="n">
+        <v>87</v>
+      </c>
+      <c r="G366" t="n">
+        <v>94</v>
+      </c>
+      <c r="H366">
         <f>F366/G366</f>
         <v/>
       </c>
-      <c r="I366" s="49">
+      <c r="I366">
         <f>IF(H366&gt;=E366,"Yes","No")</f>
         <v/>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B367" s="49" t="inlineStr">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Stryx</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Freight DIFOT</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F367" t="n">
+        <v>20</v>
+      </c>
+      <c r="G367" t="n">
+        <v>22</v>
+      </c>
+      <c r="H367">
+        <f>F367/G367</f>
+        <v/>
+      </c>
+      <c r="I367">
+        <f>IF(H367&gt;=E367,"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Below target - investigate root cause and add to next month's action plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="90" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B368" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C367" s="49" t="inlineStr">
+      <c r="C368" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E367" s="49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F367" s="49" t="n">
-        <v>162</v>
-      </c>
-      <c r="G367" s="49" t="n">
-        <v>172</v>
-      </c>
-      <c r="H367" s="49">
-        <f>F367/G367</f>
-        <v/>
-      </c>
-      <c r="I367" s="49">
-        <f>IF(H367&gt;=E367,"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="J367" s="49" t="inlineStr">
+      <c r="E368" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F368" t="n">
+        <v>169</v>
+      </c>
+      <c r="G368" t="n">
+        <v>185</v>
+      </c>
+      <c r="H368">
+        <f>F368/G368</f>
+        <v/>
+      </c>
+      <c r="I368">
+        <f>IF(H368&gt;=E368,"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="J368" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17826,7 +17849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="49" min="1" max="2"/>
@@ -17841,7 +17864,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="50">
       <c r="A3" s="81" t="inlineStr">
         <is>
@@ -18052,11 +18074,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="50">
       <c r="A15" s="84" t="inlineStr">
         <is>
@@ -18064,7 +18081,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="50">
       <c r="A17" s="81" t="inlineStr">
         <is>
@@ -20426,26 +20442,26 @@
     </row>
     <row r="112" ht="43.25" customHeight="1" s="50">
       <c r="A112" s="90" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B112" s="49" t="inlineStr">
         <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="C112" s="49" t="inlineStr">
-        <is>
-          <t>HL085007</t>
-        </is>
-      </c>
-      <c r="D112" s="49" t="inlineStr">
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C112" s="92" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="D112" s="92" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
       <c r="E112" s="49" t="inlineStr">
         <is>
-          <t>Freight DIFOT</t>
+          <t>Order Cut Off</t>
         </is>
       </c>
       <c r="F112" s="49" t="inlineStr">
@@ -20455,32 +20471,32 @@
       </c>
       <c r="G112" s="49" t="inlineStr">
         <is>
-          <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
+          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) - extension approved, not a genuine cutoff miss.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="90" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B113" s="49" t="inlineStr">
         <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="C113" s="49" t="inlineStr">
-        <is>
-          <t>4522201808</t>
-        </is>
-      </c>
-      <c r="D113" s="49" t="inlineStr">
+          <t>Salt Shark</t>
+        </is>
+      </c>
+      <c r="C113" s="92" t="inlineStr">
+        <is>
+          <t>4953</t>
+        </is>
+      </c>
+      <c r="D113" s="92" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
       <c r="E113" s="49" t="inlineStr">
         <is>
-          <t>Freight DIFOT</t>
+          <t>Order Cut Off</t>
         </is>
       </c>
       <c r="F113" s="49" t="inlineStr">
@@ -20490,32 +20506,28 @@
       </c>
       <c r="G113" s="49" t="inlineStr">
         <is>
-          <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
+          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) - extension approved, not a genuine cutoff miss.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="50">
       <c r="A114" s="90" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B114" s="49" t="inlineStr">
         <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="C114" s="49" t="inlineStr">
-        <is>
-          <t>S 122 127866</t>
-        </is>
-      </c>
-      <c r="D114" s="49" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
+          <t>Flo &amp; Frankie</t>
+        </is>
+      </c>
+      <c r="C114" s="92" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D114" s="92" t="n"/>
       <c r="E114" s="49" t="inlineStr">
         <is>
-          <t>Freight DIFOT</t>
+          <t>Order Cut Off</t>
         </is>
       </c>
       <c r="F114" s="49" t="inlineStr">
@@ -20525,40 +20537,40 @@
       </c>
       <c r="G114" s="49" t="inlineStr">
         <is>
-          <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
+          <t>Customer agreement: Flo &amp; Frankie Order Cut Off orders count as met going forward, per agreement with the customer.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="50">
       <c r="A115" s="90" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B115" s="49" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="B115" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C115" s="49" t="inlineStr">
-        <is>
-          <t>4522172931</t>
-        </is>
-      </c>
-      <c r="D115" s="49" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>HL085007</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E115" s="49" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F115" s="49" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G115" s="49" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20566,34 +20578,34 @@
     </row>
     <row r="116" ht="15" customHeight="1" s="50">
       <c r="A116" s="90" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B116" s="49" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C116" s="49" t="inlineStr">
-        <is>
-          <t>4522133734</t>
-        </is>
-      </c>
-      <c r="D116" s="49" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4522201808</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E116" s="49" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F116" s="49" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G116" s="49" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20601,34 +20613,34 @@
     </row>
     <row r="117" ht="15" customHeight="1" s="50">
       <c r="A117" s="90" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B117" s="49" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C117" s="49" t="inlineStr">
-        <is>
-          <t>4522087338</t>
-        </is>
-      </c>
-      <c r="D117" s="49" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4522172931</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E117" s="49" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F117" s="49" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G117" s="49" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20636,34 +20648,34 @@
     </row>
     <row r="118" ht="15" customHeight="1" s="50">
       <c r="A118" s="90" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B118" s="49" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="B118" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C118" s="49" t="inlineStr">
-        <is>
-          <t>4707052687</t>
-        </is>
-      </c>
-      <c r="D118" s="49" t="inlineStr">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4522133734</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E118" s="49" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F118" s="49" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G118" s="49" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20671,131 +20683,122 @@
     </row>
     <row r="119" ht="15" customHeight="1" s="50">
       <c r="A119" s="90" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B119" s="49" t="inlineStr">
-        <is>
-          <t>Salt Shark</t>
-        </is>
-      </c>
-      <c r="C119" s="92" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="D119" s="92" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>4522087338</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E119" s="49" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F119" s="49" t="inlineStr">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Freight DIFOT</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G119" s="49" t="inlineStr">
-        <is>
-          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) - extension approved, not a genuine cutoff miss.</t>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="50">
       <c r="A120" s="90" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B120" s="49" t="inlineStr">
-        <is>
-          <t>Salt Shark</t>
-        </is>
-      </c>
-      <c r="C120" s="92" t="inlineStr">
-        <is>
-          <t>4953</t>
-        </is>
-      </c>
-      <c r="D120" s="92" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4707052687</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E120" s="49" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F120" s="49" t="inlineStr">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Freight DIFOT</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G120" s="49" t="inlineStr">
-        <is>
-          <t>Order not yet dispatched; confirmed by operations to be completed and dispatched tomorrow (2 Oct 2026) - extension approved, not a genuine cutoff miss.</t>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="50">
-      <c r="A121" s="90" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B121" s="49" t="inlineStr">
-        <is>
-          <t>Flo &amp; Frankie</t>
-        </is>
-      </c>
-      <c r="C121" s="92" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="D121" s="92" t="n"/>
-      <c r="E121" s="49" t="inlineStr">
-        <is>
-          <t>Order Cut Off</t>
-        </is>
-      </c>
-      <c r="F121" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="G121" s="49" t="inlineStr">
-        <is>
-          <t>Customer agreement: Flo &amp; Frankie Order Cut Off orders count as met going forward, per agreement with the customer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="50">
-      <c r="A122" s="84" t="inlineStr">
+      <c r="A121" s="84" t="inlineStr">
         <is>
           <t>Action must be either "Exclude from calculation" or "Count as met". KPI should match the KPI name exactly (e.g. "Order Cut Off"). Order Reference must match the customer's order reference number.</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" s="50"/>
+    <row r="122" ht="15" customHeight="1" s="50"/>
+    <row r="123" ht="15" customHeight="1" s="50">
+      <c r="A123" s="81" t="inlineStr">
+        <is>
+          <t>Order Content-Based Overrides</t>
+        </is>
+      </c>
+    </row>
     <row r="124">
-      <c r="A124" s="81" t="inlineStr">
-        <is>
-          <t>Order Content-Based Overrides</t>
+      <c r="A124" s="82" t="inlineStr">
+        <is>
+          <t>Customer</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="82" t="inlineStr">
-        <is>
-          <t>Customer</t>
+      <c r="A125" s="49" t="inlineStr">
+        <is>
+          <t>Vixxen</t>
+        </is>
+      </c>
+      <c r="B125" s="49" t="inlineStr">
+        <is>
+          <t>Delivery Company Name</t>
+        </is>
+      </c>
+      <c r="C125" s="49" t="inlineStr">
+        <is>
+          <t>farmers</t>
+        </is>
+      </c>
+      <c r="D125" s="49" t="inlineStr">
+        <is>
+          <t>Next Tuesday (17:00)</t>
         </is>
       </c>
     </row>
     <row r="126" ht="126.85" customHeight="1" s="50">
       <c r="A126" s="49" t="inlineStr">
         <is>
-          <t>Vixxen</t>
+          <t>Simply Clean</t>
         </is>
       </c>
       <c r="B126" s="49" t="inlineStr">
@@ -20805,7 +20808,7 @@
       </c>
       <c r="C126" s="49" t="inlineStr">
         <is>
-          <t>farmers</t>
+          <t>briscoes</t>
         </is>
       </c>
       <c r="D126" s="49" t="inlineStr">
@@ -20817,7 +20820,7 @@
     <row r="127">
       <c r="A127" s="49" t="inlineStr">
         <is>
-          <t>Simply Clean</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="B127" s="49" t="inlineStr">
@@ -20827,73 +20830,79 @@
       </c>
       <c r="C127" s="49" t="inlineStr">
         <is>
-          <t>briscoes</t>
+          <t>farmers</t>
         </is>
       </c>
       <c r="D127" s="49" t="inlineStr">
         <is>
-          <t>Next Tuesday (17:00)</t>
-        </is>
+          <t>Next Monday (20:00)</t>
+        </is>
+      </c>
+      <c r="E127" s="83" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F127" s="83" t="n">
+        <v>46254</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="49" t="inlineStr">
         <is>
-          <t>Vixxen</t>
+          <t>Gym Equip</t>
         </is>
       </c>
       <c r="B128" s="49" t="inlineStr">
         <is>
-          <t>Delivery Company Name</t>
+          <t>All Orders</t>
         </is>
       </c>
       <c r="C128" s="49" t="inlineStr">
         <is>
-          <t>farmers</t>
+          <t>all</t>
         </is>
       </c>
       <c r="D128" s="49" t="inlineStr">
         <is>
-          <t>Next Monday (20:00)</t>
-        </is>
-      </c>
-      <c r="E128" s="83" t="n">
-        <v>46251</v>
-      </c>
+          <t>Fixed (2026-09-02 20:00)</t>
+        </is>
+      </c>
+      <c r="E128" s="83" t="n"/>
       <c r="F128" s="83" t="n">
-        <v>46254</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="129" ht="126.85" customHeight="1" s="50">
       <c r="A129" s="49" t="inlineStr">
         <is>
-          <t>Gym Equip</t>
+          <t>Simply Clean</t>
         </is>
       </c>
       <c r="B129" s="49" t="inlineStr">
         <is>
-          <t>All Orders</t>
+          <t>Delivery Company Name</t>
         </is>
       </c>
       <c r="C129" s="49" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>briscoes group</t>
         </is>
       </c>
       <c r="D129" s="49" t="inlineStr">
         <is>
-          <t>Fixed (2026-09-02 20:00)</t>
-        </is>
-      </c>
-      <c r="E129" s="83" t="n"/>
+          <t>Fixed (2026-09-18 20:00)</t>
+        </is>
+      </c>
+      <c r="E129" s="83" t="n">
+        <v>46280</v>
+      </c>
       <c r="F129" s="83" t="n">
-        <v>46266</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="50">
       <c r="A130" s="49" t="inlineStr">
         <is>
-          <t>Simply Clean</t>
+          <t>Vixxen</t>
         </is>
       </c>
       <c r="B130" s="49" t="inlineStr">
@@ -20903,83 +20912,82 @@
       </c>
       <c r="C130" s="49" t="inlineStr">
         <is>
-          <t>briscoes group</t>
+          <t>farmers</t>
         </is>
       </c>
       <c r="D130" s="49" t="inlineStr">
         <is>
-          <t>Fixed (2026-09-18 20:00)</t>
+          <t>Fixed (2026-10-13 20:00)</t>
         </is>
       </c>
       <c r="E130" s="83" t="n">
-        <v>46280</v>
+        <v>46300</v>
       </c>
       <c r="F130" s="83" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="131" ht="23.85" customHeight="1" s="50">
-      <c r="A131" s="49" t="inlineStr">
-        <is>
-          <t>Vixxen</t>
-        </is>
-      </c>
-      <c r="B131" s="49" t="inlineStr">
-        <is>
-          <t>Delivery Company Name</t>
-        </is>
-      </c>
-      <c r="C131" s="49" t="inlineStr">
-        <is>
-          <t>farmers</t>
-        </is>
-      </c>
-      <c r="D131" s="49" t="inlineStr">
-        <is>
-          <t>Fixed (2026-10-13 20:00)</t>
-        </is>
-      </c>
-      <c r="E131" s="83" t="n">
         <v>46300</v>
       </c>
-      <c r="F131" s="83" t="n">
-        <v>46300</v>
-      </c>
-    </row>
+    </row>
+    <row r="131" ht="23.85" customHeight="1" s="50"/>
     <row r="132" ht="15" customHeight="1" s="50"/>
     <row r="133" ht="15" customHeight="1" s="50"/>
     <row r="134" ht="23.85" customHeight="1" s="50"/>
-    <row r="135" ht="15" customHeight="1" s="50"/>
-    <row r="136" ht="23.85" customHeight="1" s="50">
-      <c r="A136" s="84" t="inlineStr">
+    <row r="135" ht="15" customHeight="1" s="50">
+      <c r="A135" s="84" t="inlineStr">
         <is>
           <t>Match Field currently supports "Delivery Company Name" or "All Orders" (matches every order for that customer, regardless of content - use with Contains="all"). Deadline Rule may be "Same day", "Next business day (EOD)", "Next &lt;Weekday&gt; (&lt;time&gt;)" e.g. "Next Tuesday (5pm)" - the next occurrence of that weekday on/after the order's creation date, at the given NZ time - or "Fixed (&lt;YYYY-MM-DD HH:MM&gt;)" for a single absolute deadline applied to every order in the effective window (e.g. a customer-wide stock hold/customs embargo). Leave Effective From/To blank to apply to all dates.</t>
         </is>
       </c>
     </row>
+    <row r="136" ht="23.85" customHeight="1" s="50"/>
     <row r="137" ht="23.85" customHeight="1" s="50"/>
-    <row r="138"/>
+    <row r="138">
+      <c r="A138" s="85" t="inlineStr">
+        <is>
+          <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
+        </is>
+      </c>
+    </row>
     <row r="139" ht="99.95" customHeight="1" s="50">
-      <c r="A139" s="85" t="inlineStr">
-        <is>
-          <t>Table 4: DIFOT Delivery Recipient Exceptions</t>
+      <c r="A139" s="86" t="inlineStr">
+        <is>
+          <t>Match Field</t>
+        </is>
+      </c>
+      <c r="F139" s="86" t="inlineStr">
+        <is>
+          <t>Attribute To</t>
+        </is>
+      </c>
+      <c r="G139" s="86" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="50">
-      <c r="A140" s="86" t="inlineStr">
-        <is>
-          <t>Match Field</t>
-        </is>
-      </c>
-      <c r="F140" s="86" t="inlineStr">
-        <is>
-          <t>Attribute To</t>
-        </is>
-      </c>
-      <c r="G140" s="86" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="A140" s="49" t="inlineStr">
+        <is>
+          <t>ShipTo</t>
+        </is>
+      </c>
+      <c r="B140" s="49" t="inlineStr">
+        <is>
+          <t>supercheap</t>
+        </is>
+      </c>
+      <c r="C140" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F140" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G140" s="69" t="inlineStr">
+        <is>
+          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
         </is>
       </c>
     </row>
@@ -20989,26 +20997,6 @@
           <t>ShipTo</t>
         </is>
       </c>
-      <c r="B141" s="49" t="inlineStr">
-        <is>
-          <t>supercheap</t>
-        </is>
-      </c>
-      <c r="C141" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F141" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G141" s="69" t="inlineStr">
-        <is>
-          <t>Supercheap Auto/Retail DC orders use separate pre-arranged bookings, not standard carrier tracking</t>
-        </is>
-      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="50">
       <c r="A142" s="49" t="inlineStr">
@@ -21016,6 +21004,26 @@
           <t>ShipTo</t>
         </is>
       </c>
+      <c r="B142" s="49" t="inlineStr">
+        <is>
+          <t>srg</t>
+        </is>
+      </c>
+      <c r="C142" s="49" t="inlineStr">
+        <is>
+          <t>Count as met</t>
+        </is>
+      </c>
+      <c r="F142" s="49" t="inlineStr">
+        <is>
+          <t>Oricom</t>
+        </is>
+      </c>
+      <c r="G142" s="69" t="inlineStr">
+        <is>
+          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="50">
       <c r="A143" s="49" t="inlineStr">
@@ -21025,7 +21033,7 @@
       </c>
       <c r="B143" s="49" t="inlineStr">
         <is>
-          <t>srg</t>
+          <t>repco</t>
         </is>
       </c>
       <c r="C143" s="49" t="inlineStr">
@@ -21040,189 +21048,162 @@
       </c>
       <c r="G143" s="69" t="inlineStr">
         <is>
-          <t>SRG (Super Retail Group) DC orders use separate pre-arranged bookings</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="68.65000000000001" customHeight="1" s="50">
-      <c r="A144" s="49" t="inlineStr">
-        <is>
-          <t>ShipTo</t>
-        </is>
-      </c>
-      <c r="B144" s="49" t="inlineStr">
-        <is>
-          <t>repco</t>
-        </is>
-      </c>
-      <c r="C144" s="49" t="inlineStr">
-        <is>
-          <t>Count as met</t>
-        </is>
-      </c>
-      <c r="F144" s="49" t="inlineStr">
-        <is>
-          <t>Oricom</t>
-        </is>
-      </c>
-      <c r="G144" s="69" t="inlineStr">
-        <is>
           <t>Repco (GPC-owned) orders use separate pre-arranged bookings</t>
         </is>
       </c>
     </row>
-    <row r="145"/>
-    <row r="146" ht="46.25" customHeight="1" s="50">
-      <c r="A146" s="87" t="inlineStr">
+    <row r="144" ht="68.65000000000001" customHeight="1" s="50"/>
+    <row r="145">
+      <c r="A145" s="87" t="inlineStr">
         <is>
           <t>Match Field "ShipTo" checks the Starshipit ShipTo field (case-insensitive substring match). Action "Count as met" includes these orders in the DIFOT denominator and marks them as on-time, regardless of tracking status or actual delivery date. "Attribute To" sets the customer these orders are attributed to directly (bypassing the CartonCloud join), which is needed for pre-integration DC orders where the Starshipit TheirRef does not correspond to a CC numericId. Action "Exclude" removes the order from the DIFOT calculation entirely.</t>
         </is>
       </c>
     </row>
+    <row r="146" ht="46.25" customHeight="1" s="50"/>
     <row r="147" ht="15" customHeight="1" s="50"/>
-    <row r="148" ht="15" customHeight="1" s="50"/>
+    <row r="148" ht="15" customHeight="1" s="50">
+      <c r="A148" s="85" t="inlineStr">
+        <is>
+          <t>Table 5: International Carrier SLAs</t>
+        </is>
+      </c>
+    </row>
     <row r="149" ht="15" customHeight="1" s="50">
-      <c r="A149" s="85" t="inlineStr">
-        <is>
-          <t>Table 5: International Carrier SLAs</t>
+      <c r="A149" s="86" t="inlineStr">
+        <is>
+          <t>Service Code</t>
+        </is>
+      </c>
+      <c r="B149" s="86" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="C149" s="86" t="inlineStr">
+        <is>
+          <t>Business Days</t>
+        </is>
+      </c>
+      <c r="D149" s="86" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E149" s="86" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="50">
-      <c r="A150" s="86" t="inlineStr">
-        <is>
-          <t>Service Code</t>
-        </is>
-      </c>
-      <c r="B150" s="86" t="inlineStr">
-        <is>
-          <t>Destination</t>
-        </is>
-      </c>
-      <c r="C150" s="86" t="inlineStr">
-        <is>
-          <t>Business Days</t>
-        </is>
-      </c>
-      <c r="D150" s="86" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E150" s="86" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="15" customHeight="1" s="50">
-      <c r="A151" s="49" t="inlineStr">
+      <c r="A150" s="49" t="inlineStr">
         <is>
           <t>FEDEX_INTERNATIONAL_CONNECT_PLUS</t>
         </is>
       </c>
-      <c r="B151" s="49" t="inlineStr">
+      <c r="B150" s="49" t="inlineStr">
         <is>
           <t>All international</t>
         </is>
       </c>
-      <c r="C151" s="49" t="n">
+      <c r="C150" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="D151" s="49" t="inlineStr">
+      <c r="D150" s="49" t="inlineStr">
         <is>
           <t>fedex.com/en-nz</t>
         </is>
       </c>
-      <c r="E151" s="69" t="inlineStr">
+      <c r="E150" s="69" t="inlineStr">
         <is>
           <t>FedEx FICP 'typically 2-3 business days worldwide' - using maximum per FP policy</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="15" customHeight="1" s="50"/>
-    <row r="153" ht="15" customHeight="1" s="50">
-      <c r="A153" s="87" t="inlineStr">
+    <row r="151" ht="15" customHeight="1" s="50"/>
+    <row r="152" ht="15" customHeight="1" s="50">
+      <c r="A152" s="87" t="inlineStr">
         <is>
           <t>Business Days are calculated from pickup date using add_business_days() (Mon-Fri only). To add a new carrier/destination rule, add a row here and update extract_difot.py INTL_CARRIER_DAYS dict. If a range is published (e.g. 3-5 days), always use the maximum.</t>
         </is>
       </c>
     </row>
+    <row r="153" ht="15" customHeight="1" s="50"/>
     <row r="154" ht="15" customHeight="1" s="50"/>
-    <row r="155" ht="15" customHeight="1" s="50"/>
+    <row r="155" ht="15" customHeight="1" s="50">
+      <c r="A155" s="49" t="inlineStr">
+        <is>
+          <t>Table 6: Public Holidays</t>
+        </is>
+      </c>
+    </row>
     <row r="156" ht="15" customHeight="1" s="50">
       <c r="A156" s="49" t="inlineStr">
         <is>
-          <t>Table 6: Public Holidays</t>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B156" s="49" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="50">
-      <c r="A157" s="49" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
+      <c r="A157" s="77" t="n">
+        <v>46213</v>
       </c>
       <c r="B157" s="49" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
         </is>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="50">
-      <c r="A158" s="77" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B158" s="49" t="inlineStr">
-        <is>
-          <t>Wellington Anniversary / regional public holiday — deadlines falling on this day roll to next business day</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="83" t="n"/>
-    </row>
-    <row r="160" ht="15" customHeight="1" s="50"/>
-    <row r="161">
-      <c r="A161" s="49" t="inlineStr">
+      <c r="A158" s="83" t="n"/>
+    </row>
+    <row r="159"/>
+    <row r="160" ht="15" customHeight="1" s="50">
+      <c r="A160" s="49" t="inlineStr">
         <is>
           <t>Add future public holidays here. Deadlines (Order Cut Off, required delivery date) that fall on a listed date will automatically roll forward to the next business day.</t>
         </is>
       </c>
     </row>
-    <row r="162"/>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" s="49" t="inlineStr">
+        <is>
+          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+        </is>
+      </c>
+    </row>
     <row r="163">
       <c r="A163" s="49" t="inlineStr">
         <is>
-          <t>Table 7: Operational Exceptions (Non-Business Days)</t>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B163" s="49" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="49" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
+      <c r="A164" s="83" t="n">
+        <v>46244</v>
       </c>
       <c r="B164" s="49" t="inlineStr">
         <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="83" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B165" s="49" t="inlineStr">
-        <is>
           <t>Warehouse fibre/network outage - unable to process orders all day. NOT a public holiday - an operational disruption logged here so KPI deadline calculations treat it the same way a public holiday is treated (Order Cut Off and required-delivery-date deadlines roll to the next genuine business day; no orders penalised for lack of processing today).</t>
         </is>
       </c>
     </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="49" t="inlineStr">
+    <row r="165"/>
+    <row r="166">
+      <c r="A166" s="49" t="inlineStr">
         <is>
           <t>Add one-off operational disruptions here (e.g. system outages, warehouse closures) that should count as a non-business day for KPI deadlines without being recorded as an actual public holiday. Functions identically to Table 6 for deadline-rolling purposes.</t>
         </is>
@@ -21273,7 +21254,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="82" t="inlineStr">
         <is>

--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -17266,30 +17266,30 @@
       <c r="A353" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="49" t="inlineStr">
         <is>
           <t>Aleger Studio</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E353" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F353" t="n">
+      <c r="E353" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F353" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G353" t="n">
+      <c r="G353" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H353">
+      <c r="H353" s="49">
         <f>F353/G353</f>
         <v/>
       </c>
-      <c r="I353">
+      <c r="I353" s="49">
         <f>IF(H353&gt;=E353,"Yes","No")</f>
         <v/>
       </c>
@@ -17298,34 +17298,34 @@
       <c r="A354" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="49" t="inlineStr">
         <is>
           <t>Coromandel Mountains Company Limited</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E354" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F354" t="n">
+      <c r="E354" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F354" s="49" t="n">
         <v>36</v>
       </c>
-      <c r="G354" t="n">
+      <c r="G354" s="49" t="n">
         <v>38</v>
       </c>
-      <c r="H354">
+      <c r="H354" s="49">
         <f>F354/G354</f>
         <v/>
       </c>
-      <c r="I354">
+      <c r="I354" s="49">
         <f>IF(H354&gt;=E354,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J354" t="inlineStr">
+      <c r="J354" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17335,34 +17335,34 @@
       <c r="A355" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="49" t="inlineStr">
         <is>
           <t>EcoPallets</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E355" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F355" t="n">
+      <c r="E355" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F355" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G355" t="n">
+      <c r="G355" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H355">
+      <c r="H355" s="49">
         <f>F355/G355</f>
         <v/>
       </c>
-      <c r="I355">
+      <c r="I355" s="49">
         <f>IF(H355&gt;=E355,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J355" t="inlineStr">
+      <c r="J355" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17372,34 +17372,34 @@
       <c r="A356" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="49" t="inlineStr">
         <is>
           <t>Flo &amp; Frankie</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E356" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F356" t="n">
+      <c r="E356" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F356" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="G356" t="n">
+      <c r="G356" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="H356">
+      <c r="H356" s="49">
         <f>F356/G356</f>
         <v/>
       </c>
-      <c r="I356">
+      <c r="I356" s="49">
         <f>IF(H356&gt;=E356,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J356" t="inlineStr">
+      <c r="J356" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17409,34 +17409,34 @@
       <c r="A357" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B357" s="49" t="inlineStr">
         <is>
           <t>Gym Equip</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E357" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F357" t="n">
+      <c r="E357" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F357" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="G357" t="n">
+      <c r="G357" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="H357">
+      <c r="H357" s="49">
         <f>F357/G357</f>
         <v/>
       </c>
-      <c r="I357">
+      <c r="I357" s="49">
         <f>IF(H357&gt;=E357,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J357" t="inlineStr">
+      <c r="J357" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17446,30 +17446,30 @@
       <c r="A358" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="49" t="inlineStr">
         <is>
           <t>Interior Images</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E358" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F358" t="n">
+      <c r="E358" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F358" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G358" t="n">
+      <c r="G358" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H358">
+      <c r="H358" s="49">
         <f>F358/G358</f>
         <v/>
       </c>
-      <c r="I358">
+      <c r="I358" s="49">
         <f>IF(H358&gt;=E358,"Yes","No")</f>
         <v/>
       </c>
@@ -17478,34 +17478,34 @@
       <c r="A359" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="49" t="inlineStr">
         <is>
           <t>Jock Freight - SECA</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E359" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F359" t="n">
+      <c r="E359" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F359" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="G359" t="n">
+      <c r="G359" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="H359">
+      <c r="H359" s="49">
         <f>F359/G359</f>
         <v/>
       </c>
-      <c r="I359">
+      <c r="I359" s="49">
         <f>IF(H359&gt;=E359,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J359" t="inlineStr">
+      <c r="J359" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17515,30 +17515,30 @@
       <c r="A360" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B360" s="49" t="inlineStr">
         <is>
           <t>Logwin - Sikla</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E360" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F360" t="n">
+      <c r="E360" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F360" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G360" t="n">
+      <c r="G360" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H360">
+      <c r="H360" s="49">
         <f>F360/G360</f>
         <v/>
       </c>
-      <c r="I360">
+      <c r="I360" s="49">
         <f>IF(H360&gt;=E360,"Yes","No")</f>
         <v/>
       </c>
@@ -17547,30 +17547,30 @@
       <c r="A361" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B361" s="49" t="inlineStr">
         <is>
           <t>Made Group NZ</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E361" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F361" t="n">
+      <c r="E361" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F361" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G361" t="n">
+      <c r="G361" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H361">
+      <c r="H361" s="49">
         <f>F361/G361</f>
         <v/>
       </c>
-      <c r="I361">
+      <c r="I361" s="49">
         <f>IF(H361&gt;=E361,"Yes","No")</f>
         <v/>
       </c>
@@ -17579,30 +17579,30 @@
       <c r="A362" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B362" s="49" t="inlineStr">
         <is>
           <t>May Eleven NZ</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E362" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F362" t="n">
+      <c r="E362" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F362" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G362" t="n">
+      <c r="G362" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="H362">
+      <c r="H362" s="49">
         <f>F362/G362</f>
         <v/>
       </c>
-      <c r="I362">
+      <c r="I362" s="49">
         <f>IF(H362&gt;=E362,"Yes","No")</f>
         <v/>
       </c>
@@ -17611,34 +17611,34 @@
       <c r="A363" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B363" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E363" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F363" t="n">
+      <c r="E363" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F363" s="49" t="n">
         <v>84</v>
       </c>
-      <c r="G363" t="n">
+      <c r="G363" s="49" t="n">
         <v>91</v>
       </c>
-      <c r="H363">
+      <c r="H363" s="49">
         <f>F363/G363</f>
         <v/>
       </c>
-      <c r="I363">
+      <c r="I363" s="49">
         <f>IF(H363&gt;=E363,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J363" t="inlineStr">
+      <c r="J363" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17648,34 +17648,34 @@
       <c r="A364" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B364" s="49" t="inlineStr">
         <is>
           <t>Purify Me</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E364" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F364" t="n">
+      <c r="E364" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F364" s="49" t="n">
         <v>48</v>
       </c>
-      <c r="G364" t="n">
+      <c r="G364" s="49" t="n">
         <v>53</v>
       </c>
-      <c r="H364">
+      <c r="H364" s="49">
         <f>F364/G364</f>
         <v/>
       </c>
-      <c r="I364">
+      <c r="I364" s="49">
         <f>IF(H364&gt;=E364,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J364" t="inlineStr">
+      <c r="J364" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17685,30 +17685,30 @@
       <c r="A365" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="49" t="inlineStr">
         <is>
           <t>Salt Shark</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E365" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F365" t="n">
+      <c r="E365" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F365" s="49" t="n">
         <v>41</v>
       </c>
-      <c r="G365" t="n">
+      <c r="G365" s="49" t="n">
         <v>43</v>
       </c>
-      <c r="H365">
+      <c r="H365" s="49">
         <f>F365/G365</f>
         <v/>
       </c>
-      <c r="I365">
+      <c r="I365" s="49">
         <f>IF(H365&gt;=E365,"Yes","No")</f>
         <v/>
       </c>
@@ -17717,34 +17717,34 @@
       <c r="A366" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="49" t="inlineStr">
         <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E366" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F366" t="n">
+      <c r="E366" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F366" s="49" t="n">
         <v>87</v>
       </c>
-      <c r="G366" t="n">
+      <c r="G366" s="49" t="n">
         <v>94</v>
       </c>
-      <c r="H366">
+      <c r="H366" s="49">
         <f>F366/G366</f>
         <v/>
       </c>
-      <c r="I366">
+      <c r="I366" s="49">
         <f>IF(H366&gt;=E366,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J366" t="inlineStr">
+      <c r="J366" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17754,34 +17754,34 @@
       <c r="A367" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="49" t="inlineStr">
         <is>
           <t>Stryx</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E367" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F367" t="n">
+      <c r="E367" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F367" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="G367" t="n">
+      <c r="G367" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="H367">
+      <c r="H367" s="49">
         <f>F367/G367</f>
         <v/>
       </c>
-      <c r="I367">
+      <c r="I367" s="49">
         <f>IF(H367&gt;=E367,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J367" t="inlineStr">
+      <c r="J367" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17791,34 +17791,34 @@
       <c r="A368" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="49" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E368" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F368" t="n">
+      <c r="E368" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F368" s="49" t="n">
         <v>169</v>
       </c>
-      <c r="G368" t="n">
+      <c r="G368" s="49" t="n">
         <v>185</v>
       </c>
-      <c r="H368">
+      <c r="H368" s="49">
         <f>F368/G368</f>
         <v/>
       </c>
-      <c r="I368">
+      <c r="I368" s="49">
         <f>IF(H368&gt;=E368,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J368" t="inlineStr">
+      <c r="J368" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -18730,10 +18730,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="50">
       <c r="A40" s="77" t="n">
         <v>46196</v>
@@ -20545,32 +20541,32 @@
       <c r="A115" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="49" t="inlineStr">
         <is>
           <t>HL085007</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20580,32 +20576,32 @@
       <c r="A116" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="49" t="inlineStr">
         <is>
           <t>4522201808</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G116" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20615,32 +20611,32 @@
       <c r="A117" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="49" t="inlineStr">
         <is>
           <t>4522172931</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20650,32 +20646,32 @@
       <c r="A118" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="49" t="inlineStr">
         <is>
           <t>4522133734</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20685,32 +20681,32 @@
       <c r="A119" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="49" t="inlineStr">
         <is>
           <t>4522087338</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20720,32 +20716,32 @@
       <c r="A120" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="49" t="inlineStr">
         <is>
           <t>4707052687</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G120" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -21163,7 +21159,6 @@
     <row r="158" ht="15" customHeight="1" s="50">
       <c r="A158" s="83" t="n"/>
     </row>
-    <row r="159"/>
     <row r="160" ht="15" customHeight="1" s="50">
       <c r="A160" s="49" t="inlineStr">
         <is>
@@ -21171,7 +21166,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162">
       <c r="A162" s="49" t="inlineStr">
         <is>
@@ -21201,7 +21195,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="A166" s="49" t="inlineStr">
         <is>
@@ -21230,7 +21223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="49" min="1" max="1"/>
@@ -21488,6 +21481,52 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="91" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>Cross-labelled cartons - items shipped with the wrong carton labels</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>Cross-labelled cartons - items shipped with the wrong carton labels</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>

--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -17266,30 +17266,30 @@
       <c r="A353" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="49" t="inlineStr">
         <is>
           <t>Aleger Studio</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E353" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F353" t="n">
+      <c r="E353" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F353" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G353" t="n">
+      <c r="G353" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H353">
+      <c r="H353" s="49">
         <f>F353/G353</f>
         <v/>
       </c>
-      <c r="I353">
+      <c r="I353" s="49">
         <f>IF(H353&gt;=E353,"Yes","No")</f>
         <v/>
       </c>
@@ -17298,34 +17298,34 @@
       <c r="A354" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="49" t="inlineStr">
         <is>
           <t>Coromandel Mountains Company Limited</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E354" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F354" t="n">
+      <c r="E354" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F354" s="49" t="n">
         <v>36</v>
       </c>
-      <c r="G354" t="n">
+      <c r="G354" s="49" t="n">
         <v>38</v>
       </c>
-      <c r="H354">
+      <c r="H354" s="49">
         <f>F354/G354</f>
         <v/>
       </c>
-      <c r="I354">
+      <c r="I354" s="49">
         <f>IF(H354&gt;=E354,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J354" t="inlineStr">
+      <c r="J354" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17335,34 +17335,34 @@
       <c r="A355" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="49" t="inlineStr">
         <is>
           <t>EcoPallets</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E355" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F355" t="n">
+      <c r="E355" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F355" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G355" t="n">
+      <c r="G355" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H355">
+      <c r="H355" s="49">
         <f>F355/G355</f>
         <v/>
       </c>
-      <c r="I355">
+      <c r="I355" s="49">
         <f>IF(H355&gt;=E355,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J355" t="inlineStr">
+      <c r="J355" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17372,34 +17372,34 @@
       <c r="A356" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="49" t="inlineStr">
         <is>
           <t>Flo &amp; Frankie</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E356" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F356" t="n">
+      <c r="E356" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F356" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="G356" t="n">
+      <c r="G356" s="49" t="n">
         <v>13</v>
       </c>
-      <c r="H356">
+      <c r="H356" s="49">
         <f>F356/G356</f>
         <v/>
       </c>
-      <c r="I356">
+      <c r="I356" s="49">
         <f>IF(H356&gt;=E356,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J356" t="inlineStr">
+      <c r="J356" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17409,34 +17409,34 @@
       <c r="A357" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B357" s="49" t="inlineStr">
         <is>
           <t>Gym Equip</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E357" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F357" t="n">
+      <c r="E357" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F357" s="49" t="n">
         <v>17</v>
       </c>
-      <c r="G357" t="n">
+      <c r="G357" s="49" t="n">
         <v>19</v>
       </c>
-      <c r="H357">
+      <c r="H357" s="49">
         <f>F357/G357</f>
         <v/>
       </c>
-      <c r="I357">
+      <c r="I357" s="49">
         <f>IF(H357&gt;=E357,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J357" t="inlineStr">
+      <c r="J357" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17446,30 +17446,30 @@
       <c r="A358" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="49" t="inlineStr">
         <is>
           <t>Interior Images</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E358" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F358" t="n">
+      <c r="E358" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F358" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G358" t="n">
+      <c r="G358" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H358">
+      <c r="H358" s="49">
         <f>F358/G358</f>
         <v/>
       </c>
-      <c r="I358">
+      <c r="I358" s="49">
         <f>IF(H358&gt;=E358,"Yes","No")</f>
         <v/>
       </c>
@@ -17478,34 +17478,34 @@
       <c r="A359" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="49" t="inlineStr">
         <is>
           <t>Jock Freight - SECA</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E359" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F359" t="n">
+      <c r="E359" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F359" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="G359" t="n">
+      <c r="G359" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="H359">
+      <c r="H359" s="49">
         <f>F359/G359</f>
         <v/>
       </c>
-      <c r="I359">
+      <c r="I359" s="49">
         <f>IF(H359&gt;=E359,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J359" t="inlineStr">
+      <c r="J359" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17515,30 +17515,30 @@
       <c r="A360" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B360" s="49" t="inlineStr">
         <is>
           <t>Logwin - Sikla</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E360" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F360" t="n">
+      <c r="E360" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F360" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="G360" t="n">
+      <c r="G360" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H360">
+      <c r="H360" s="49">
         <f>F360/G360</f>
         <v/>
       </c>
-      <c r="I360">
+      <c r="I360" s="49">
         <f>IF(H360&gt;=E360,"Yes","No")</f>
         <v/>
       </c>
@@ -17547,30 +17547,30 @@
       <c r="A361" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B361" s="49" t="inlineStr">
         <is>
           <t>Made Group NZ</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E361" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F361" t="n">
+      <c r="E361" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F361" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G361" t="n">
+      <c r="G361" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H361">
+      <c r="H361" s="49">
         <f>F361/G361</f>
         <v/>
       </c>
-      <c r="I361">
+      <c r="I361" s="49">
         <f>IF(H361&gt;=E361,"Yes","No")</f>
         <v/>
       </c>
@@ -17579,30 +17579,30 @@
       <c r="A362" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B362" s="49" t="inlineStr">
         <is>
           <t>May Eleven NZ</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E362" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F362" t="n">
+      <c r="E362" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F362" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G362" t="n">
+      <c r="G362" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="H362">
+      <c r="H362" s="49">
         <f>F362/G362</f>
         <v/>
       </c>
-      <c r="I362">
+      <c r="I362" s="49">
         <f>IF(H362&gt;=E362,"Yes","No")</f>
         <v/>
       </c>
@@ -17611,34 +17611,34 @@
       <c r="A363" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B363" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E363" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F363" t="n">
+      <c r="E363" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F363" s="49" t="n">
         <v>84</v>
       </c>
-      <c r="G363" t="n">
+      <c r="G363" s="49" t="n">
         <v>91</v>
       </c>
-      <c r="H363">
+      <c r="H363" s="49">
         <f>F363/G363</f>
         <v/>
       </c>
-      <c r="I363">
+      <c r="I363" s="49">
         <f>IF(H363&gt;=E363,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J363" t="inlineStr">
+      <c r="J363" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17648,34 +17648,34 @@
       <c r="A364" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B364" s="49" t="inlineStr">
         <is>
           <t>Purify Me</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E364" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F364" t="n">
+      <c r="E364" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F364" s="49" t="n">
         <v>48</v>
       </c>
-      <c r="G364" t="n">
+      <c r="G364" s="49" t="n">
         <v>53</v>
       </c>
-      <c r="H364">
+      <c r="H364" s="49">
         <f>F364/G364</f>
         <v/>
       </c>
-      <c r="I364">
+      <c r="I364" s="49">
         <f>IF(H364&gt;=E364,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J364" t="inlineStr">
+      <c r="J364" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17685,30 +17685,30 @@
       <c r="A365" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="49" t="inlineStr">
         <is>
           <t>Salt Shark</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E365" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F365" t="n">
+      <c r="E365" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F365" s="49" t="n">
         <v>41</v>
       </c>
-      <c r="G365" t="n">
+      <c r="G365" s="49" t="n">
         <v>43</v>
       </c>
-      <c r="H365">
+      <c r="H365" s="49">
         <f>F365/G365</f>
         <v/>
       </c>
-      <c r="I365">
+      <c r="I365" s="49">
         <f>IF(H365&gt;=E365,"Yes","No")</f>
         <v/>
       </c>
@@ -17717,34 +17717,34 @@
       <c r="A366" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="49" t="inlineStr">
         <is>
           <t>Simply Clean</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E366" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F366" t="n">
+      <c r="E366" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F366" s="49" t="n">
         <v>87</v>
       </c>
-      <c r="G366" t="n">
+      <c r="G366" s="49" t="n">
         <v>94</v>
       </c>
-      <c r="H366">
+      <c r="H366" s="49">
         <f>F366/G366</f>
         <v/>
       </c>
-      <c r="I366">
+      <c r="I366" s="49">
         <f>IF(H366&gt;=E366,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J366" t="inlineStr">
+      <c r="J366" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17754,34 +17754,34 @@
       <c r="A367" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="49" t="inlineStr">
         <is>
           <t>Stryx</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E367" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F367" t="n">
+      <c r="E367" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F367" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="G367" t="n">
+      <c r="G367" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="H367">
+      <c r="H367" s="49">
         <f>F367/G367</f>
         <v/>
       </c>
-      <c r="I367">
+      <c r="I367" s="49">
         <f>IF(H367&gt;=E367,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J367" t="inlineStr">
+      <c r="J367" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -17791,34 +17791,34 @@
       <c r="A368" s="90" t="n">
         <v>46266</v>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="49" t="inlineStr">
         <is>
           <t>Vixxen</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="E368" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F368" t="n">
+      <c r="E368" s="49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F368" s="49" t="n">
         <v>169</v>
       </c>
-      <c r="G368" t="n">
+      <c r="G368" s="49" t="n">
         <v>185</v>
       </c>
-      <c r="H368">
+      <c r="H368" s="49">
         <f>F368/G368</f>
         <v/>
       </c>
-      <c r="I368">
+      <c r="I368" s="49">
         <f>IF(H368&gt;=E368,"Yes","No")</f>
         <v/>
       </c>
-      <c r="J368" t="inlineStr">
+      <c r="J368" s="49" t="inlineStr">
         <is>
           <t>Below target - investigate root cause and add to next month's action plan</t>
         </is>
@@ -18730,10 +18730,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" ht="15" customHeight="1" s="50">
       <c r="A40" s="77" t="n">
         <v>46196</v>
@@ -20545,32 +20541,32 @@
       <c r="A115" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="49" t="inlineStr">
         <is>
           <t>HL085007</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20580,32 +20576,32 @@
       <c r="A116" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="49" t="inlineStr">
         <is>
           <t>4522201808</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G116" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20615,32 +20611,32 @@
       <c r="A117" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="49" t="inlineStr">
         <is>
           <t>4522172931</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20650,32 +20646,32 @@
       <c r="A118" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="49" t="inlineStr">
         <is>
           <t>4522133734</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20685,32 +20681,32 @@
       <c r="A119" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="49" t="inlineStr">
         <is>
           <t>4522087338</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20720,32 +20716,32 @@
       <c r="A120" s="90" t="n">
         <v>46303</v>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="49" t="inlineStr">
         <is>
           <t>Oricom</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="49" t="inlineStr">
         <is>
           <t>4707052687</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="49" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="49" t="inlineStr">
         <is>
           <t>Freight DIFOT</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="49" t="inlineStr">
         <is>
           <t>Count as met</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G120" s="49" t="inlineStr">
         <is>
           <t>DC recipient exception - pre-arranged booking, excluded from avg delivery days</t>
         </is>
@@ -20927,7 +20923,34 @@
         <v>46300</v>
       </c>
     </row>
-    <row r="131" ht="23.85" customHeight="1" s="50"/>
+    <row r="131" ht="23.85" customHeight="1" s="50">
+      <c r="A131" s="49" t="inlineStr">
+        <is>
+          <t>Made Group NZ</t>
+        </is>
+      </c>
+      <c r="B131" s="49" t="inlineStr">
+        <is>
+          <t>All Orders</t>
+        </is>
+      </c>
+      <c r="C131" s="49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D131" s="49" t="inlineStr">
+        <is>
+          <t>Fixed (2026-10-16 13:00)</t>
+        </is>
+      </c>
+      <c r="E131" s="83" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F131" s="83" t="n">
+        <v>46309</v>
+      </c>
+    </row>
     <row r="132" ht="15" customHeight="1" s="50"/>
     <row r="133" ht="15" customHeight="1" s="50"/>
     <row r="134" ht="23.85" customHeight="1" s="50"/>
@@ -21163,7 +21186,6 @@
     <row r="158" ht="15" customHeight="1" s="50">
       <c r="A158" s="83" t="n"/>
     </row>
-    <row r="159"/>
     <row r="160" ht="15" customHeight="1" s="50">
       <c r="A160" s="49" t="inlineStr">
         <is>
@@ -21171,7 +21193,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162">
       <c r="A162" s="49" t="inlineStr">
         <is>
@@ -21201,7 +21222,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
     <row r="166">
       <c r="A166" s="49" t="inlineStr">
         <is>

--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -21230,7 +21230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="49" min="1" max="1"/>
@@ -21488,6 +21488,52 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="91" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>Cross-labelled cartons</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>Cross-labelled cartons</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>

--- a/pipeline/kpi_dashboard.xlsx
+++ b/pipeline/kpi_dashboard.xlsx
@@ -21230,7 +21230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="49" min="1" max="1"/>
@@ -21488,6 +21488,52 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="91" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>Cross-labelled cartons</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Coromandel Mountains Company Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>Cross-labelled cartons</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
